--- a/database/event/5454/event_5454_evp_summary.xlsx
+++ b/database/event/5454/event_5454_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9802</v>
+        <v>4.8767</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8108</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5905</v>
+        <v>1.499</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9802</v>
+        <v>4.8767</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9802</v>
+        <v>4.8767</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5058</v>
+        <v>5.3436</v>
       </c>
       <c r="I2" t="n">
         <v>5.7142</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7288</v>
+        <v>4.5975</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7698</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.489</v>
+        <v>1.3877</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7288</v>
+        <v>4.5975</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7288</v>
+        <v>4.5975</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1117</v>
+        <v>4.9058</v>
       </c>
       <c r="I3" t="n">
         <v>5.3796</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5092</v>
+        <v>4.4196</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7341</v>
+        <v>0.7195</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4003</v>
+        <v>1.3169</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5092</v>
+        <v>4.4196</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5092</v>
+        <v>4.4196</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7674</v>
+        <v>4.6269</v>
       </c>
       <c r="I4" t="n">
         <v>4.9478</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1194</v>
+        <v>4.0703</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6706</v>
+        <v>0.6626</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2428</v>
+        <v>1.1777</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1194</v>
+        <v>4.0703</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1194</v>
+        <v>4.0703</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1562</v>
+        <v>4.0792</v>
       </c>
       <c r="I5" t="n">
         <v>4.2538</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9288</v>
+        <v>3.885</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6325</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1658</v>
+        <v>1.1039</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9288</v>
+        <v>3.885</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9288</v>
+        <v>3.885</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9288</v>
+        <v>3.885</v>
       </c>
       <c r="I6" t="n">
         <v>3.9839</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8396</v>
+        <v>3.7265</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6251</v>
+        <v>0.6067</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1298</v>
+        <v>1.0407</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8396</v>
+        <v>3.7265</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8396</v>
+        <v>3.7265</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8396</v>
+        <v>3.7265</v>
       </c>
       <c r="I7" t="n">
         <v>3.9849</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5518</v>
+        <v>3.4087</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5782</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0135</v>
+        <v>0.9141</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5518</v>
+        <v>3.4087</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5518</v>
+        <v>3.4087</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5518</v>
+        <v>3.4087</v>
       </c>
       <c r="I8" t="n">
         <v>3.7379</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8725</v>
+        <v>2.7568</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4676</v>
+        <v>0.4488</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7391</v>
+        <v>0.6544</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8725</v>
+        <v>2.7568</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8725</v>
+        <v>2.7568</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8725</v>
+        <v>2.7568</v>
       </c>
       <c r="I9" t="n">
         <v>3.023</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1996</v>
+        <v>2.1669</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3581</v>
+        <v>0.3528</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4672</v>
+        <v>0.4194</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1996</v>
+        <v>2.1669</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1996</v>
+        <v>2.1669</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1996</v>
+        <v>2.1669</v>
       </c>
       <c r="I10" t="n">
         <v>2.2408</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1386</v>
+        <v>2.1147</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3482</v>
+        <v>0.3443</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4426</v>
+        <v>0.3986</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1386</v>
+        <v>2.1147</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1386</v>
+        <v>2.1147</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1386</v>
+        <v>2.1147</v>
       </c>
       <c r="I11" t="n">
         <v>2.1686</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8376</v>
+        <v>1.8308</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2992</v>
+        <v>0.2981</v>
       </c>
       <c r="D12" t="n">
-        <v>0.321</v>
+        <v>0.2855</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8376</v>
+        <v>1.8308</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8376</v>
+        <v>1.8308</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8376</v>
+        <v>1.8308</v>
       </c>
       <c r="I12" t="n">
         <v>1.8462</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8165</v>
+        <v>1.7829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2957</v>
+        <v>0.2903</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3125</v>
+        <v>0.2664</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8165</v>
+        <v>1.7829</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8165</v>
+        <v>1.7829</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8165</v>
+        <v>1.7829</v>
       </c>
       <c r="I13" t="n">
         <v>1.8592</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7319</v>
+        <v>1.6808</v>
       </c>
       <c r="C14" t="n">
-        <v>0.282</v>
+        <v>0.2736</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2783</v>
+        <v>0.2257</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7319</v>
+        <v>1.6808</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7319</v>
+        <v>1.6808</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7319</v>
+        <v>1.6808</v>
       </c>
       <c r="I14" t="n">
         <v>1.7974</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6862</v>
+        <v>1.655</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2745</v>
+        <v>0.2694</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2598</v>
+        <v>0.2154</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6862</v>
+        <v>1.655</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6862</v>
+        <v>1.655</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6862</v>
+        <v>1.655</v>
       </c>
       <c r="I15" t="n">
         <v>1.7258</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5737</v>
+        <v>1.5562</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2562</v>
+        <v>0.2533</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2144</v>
+        <v>0.1761</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5737</v>
+        <v>1.5562</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5737</v>
+        <v>1.5562</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5737</v>
+        <v>1.5562</v>
       </c>
       <c r="I16" t="n">
         <v>1.5958</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3607</v>
+        <v>1.3347</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2215</v>
+        <v>0.2173</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1283</v>
+        <v>0.0878</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3607</v>
+        <v>1.3347</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3607</v>
+        <v>1.3347</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3607</v>
+        <v>1.3347</v>
       </c>
       <c r="I17" t="n">
-        <v>1.432</v>
+        <v>1.3686</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.432</v>
+        <v>1.3686</v>
       </c>
       <c r="N17" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3497</v>
+        <v>1.3059</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2197</v>
+        <v>0.2126</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1239</v>
+        <v>0.0764</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3497</v>
+        <v>1.3059</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3497</v>
+        <v>1.3059</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3497</v>
+        <v>1.3059</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3686</v>
+        <v>1.432</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3686</v>
+        <v>1.432</v>
       </c>
       <c r="N18" t="n">
-        <v>166</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>0.1681</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0041</v>
+        <v>-0.0324</v>
       </c>
       <c r="E19" t="n">
         <v>1.0328</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9341</v>
+        <v>0.9237</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1521</v>
+        <v>0.1504</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.044</v>
+        <v>-0.0759</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9341</v>
+        <v>0.9237</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9341</v>
+        <v>0.9237</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9341</v>
+        <v>0.9237</v>
       </c>
       <c r="I20" t="n">
         <v>0.9472</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7116</v>
+        <v>0.7089</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1158</v>
+        <v>0.1154</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1339</v>
+        <v>-0.1615</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7116</v>
+        <v>0.7089</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7116</v>
+        <v>0.7089</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7116</v>
+        <v>0.7089</v>
       </c>
       <c r="I21" t="n">
         <v>0.7149</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6926</v>
+        <v>0.6849</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1128</v>
+        <v>0.1115</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1416</v>
+        <v>-0.171</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6926</v>
+        <v>0.6849</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6926</v>
+        <v>0.6849</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6926</v>
+        <v>0.6849</v>
       </c>
       <c r="I22" t="n">
         <v>0.7023</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6858</v>
+        <v>0.6781</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1116</v>
+        <v>0.1104</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1443</v>
+        <v>-0.1738</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6858</v>
+        <v>0.6781</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6858</v>
+        <v>0.6781</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6858</v>
+        <v>0.6781</v>
       </c>
       <c r="I23" t="n">
         <v>0.6954</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5864</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0969</v>
+        <v>0.0955</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1809</v>
+        <v>-0.2103</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5864</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5864</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5864</v>
       </c>
       <c r="I24" t="n">
         <v>0.6064000000000001</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.105</v>
+        <v>0.1046</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0171</v>
+        <v>0.017</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3789</v>
+        <v>-0.4022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.105</v>
+        <v>0.1046</v>
       </c>
       <c r="F25" t="n">
-        <v>0.105</v>
+        <v>0.1046</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.105</v>
+        <v>0.1046</v>
       </c>
       <c r="I25" t="n">
         <v>0.1055</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0571</v>
+        <v>-0.0565</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4444</v>
+        <v>-0.4664</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0571</v>
+        <v>-0.0565</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0571</v>
+        <v>-0.0565</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0571</v>
+        <v>-0.0565</v>
       </c>
       <c r="I26" t="n">
         <v>-0.0579</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4751</v>
+        <v>-0.468</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0762</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6133</v>
+        <v>-0.6304</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4751</v>
+        <v>-0.468</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4751</v>
+        <v>-0.468</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4751</v>
+        <v>-0.468</v>
       </c>
       <c r="I27" t="n">
         <v>-0.484</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5505</v>
+        <v>-0.5343</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0896</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6438</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5505</v>
+        <v>-0.5343</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5505</v>
+        <v>-0.5343</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5505</v>
+        <v>-0.5343</v>
       </c>
       <c r="I28" t="n">
         <v>-0.5713</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5915</v>
+        <v>-0.5849</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0963</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6603</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5915</v>
+        <v>-0.5849</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5915</v>
+        <v>-0.5849</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5915</v>
+        <v>-0.5849</v>
       </c>
       <c r="I29" t="n">
         <v>-0.5998</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1032</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6775</v>
+        <v>-0.6965</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6341</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1198</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7187</v>
+        <v>-0.7372</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7361</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9329</v>
+        <v>-0.8953</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1519</v>
+        <v>-0.1458</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7982</v>
+        <v>-0.8006</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9329</v>
+        <v>-0.8953</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9329</v>
+        <v>-0.8953</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9329</v>
+        <v>-0.8953</v>
       </c>
       <c r="I32" t="n">
         <v>-0.9818</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1682</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8387</v>
+        <v>-0.8555</v>
       </c>
       <c r="E33" t="n">
         <v>-1.033</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0831</v>
+        <v>-1.079</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1763</v>
+        <v>-0.1757</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8589</v>
+        <v>-0.8738</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0831</v>
+        <v>-1.079</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0831</v>
+        <v>-1.079</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0831</v>
+        <v>-1.079</v>
       </c>
       <c r="I34" t="n">
         <v>-1.0881</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1299</v>
+        <v>-1.1131</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1839</v>
+        <v>-0.1812</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8778</v>
+        <v>-0.8874</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1299</v>
+        <v>-1.1131</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1299</v>
+        <v>-1.1131</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1299</v>
+        <v>-1.1131</v>
       </c>
       <c r="I35" t="n">
         <v>-1.1511</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2299</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9917</v>
+        <v>-1.0064</v>
       </c>
       <c r="E36" t="n">
         <v>-1.4119</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6081</v>
+        <v>-1.6021</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2618</v>
+        <v>-0.2608</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.071</v>
+        <v>-1.0822</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6081</v>
+        <v>-1.6021</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6081</v>
+        <v>-1.6021</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6081</v>
+        <v>-1.6021</v>
       </c>
       <c r="I37" t="n">
         <v>-1.6156</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7791</v>
+        <v>-1.7527</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2896</v>
+        <v>-0.2853</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1401</v>
+        <v>-1.1422</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7791</v>
+        <v>-1.7527</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7791</v>
+        <v>-1.7527</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7791</v>
+        <v>-1.7527</v>
       </c>
       <c r="I38" t="n">
         <v>-1.8125</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8139</v>
+        <v>-1.7936</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2953</v>
+        <v>-0.292</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1541</v>
+        <v>-1.1585</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8139</v>
+        <v>-1.7936</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8139</v>
+        <v>-1.7936</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8139</v>
+        <v>-1.7936</v>
       </c>
       <c r="I39" t="n">
         <v>-1.8393</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2657</v>
+        <v>-2.2237</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3689</v>
+        <v>-0.362</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3367</v>
+        <v>-1.3298</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2657</v>
+        <v>-2.2237</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2657</v>
+        <v>-2.2237</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2657</v>
+        <v>-2.2237</v>
       </c>
       <c r="I40" t="n">
         <v>-2.3189</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3945</v>
+        <v>-2.3501</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3898</v>
+        <v>-0.3826</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3887</v>
+        <v>-1.3802</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3945</v>
+        <v>-2.3501</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3945</v>
+        <v>-2.3501</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3945</v>
+        <v>-2.3501</v>
       </c>
       <c r="I41" t="n">
         <v>-2.4507</v>

--- a/database/event/5454/event_5454_evp_summary.xlsx
+++ b/database/event/5454/event_5454_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.8767</v>
+        <v>3.5505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.578</v>
       </c>
       <c r="D2" t="n">
-        <v>1.499</v>
+        <v>0.9649</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8767</v>
+        <v>3.5505</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8767</v>
+        <v>3.5505</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3436</v>
+        <v>4.4365</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7142</v>
+        <v>6.1245</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7142</v>
+        <v>6.1245</v>
       </c>
       <c r="N2" t="n">
         <v>298</v>
@@ -538,47 +538,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5975</v>
+        <v>3.3524</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.5458</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3877</v>
+        <v>0.8754</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5975</v>
+        <v>3.3524</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5975</v>
+        <v>3.3524</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9058</v>
+        <v>4.0014</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3796</v>
+        <v>4.5157</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3796</v>
+        <v>4.5157</v>
       </c>
       <c r="N3" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4196</v>
+        <v>3.3311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7195</v>
+        <v>0.5423</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3169</v>
+        <v>0.8658</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4196</v>
+        <v>3.3311</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4196</v>
+        <v>3.3311</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6269</v>
+        <v>3.9547</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9478</v>
+        <v>5.4594</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9478</v>
+        <v>5.4594</v>
       </c>
       <c r="N4" t="n">
         <v>298</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0703</v>
+        <v>3.2967</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6626</v>
+        <v>0.5367</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1777</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0703</v>
+        <v>3.2967</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0703</v>
+        <v>3.2967</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0792</v>
+        <v>3.8792</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2538</v>
+        <v>4.7452</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2538</v>
+        <v>4.7452</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -676,216 +676,216 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.885</v>
+        <v>3.292</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6325</v>
+        <v>0.5359</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1039</v>
+        <v>0.8482</v>
       </c>
       <c r="E6" t="n">
-        <v>3.885</v>
+        <v>3.292</v>
       </c>
       <c r="F6" t="n">
-        <v>3.885</v>
+        <v>3.292</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.885</v>
+        <v>3.869</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9839</v>
+        <v>6.0275</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9839</v>
+        <v>6.0275</v>
       </c>
       <c r="N6" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7265</v>
+        <v>3.057</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6067</v>
+        <v>0.4977</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0407</v>
+        <v>0.7421</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7265</v>
+        <v>3.057</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7265</v>
+        <v>3.057</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7265</v>
+        <v>3.3529</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9849</v>
+        <v>5.2235</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>298</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9849</v>
+        <v>5.2235</v>
       </c>
       <c r="N7" t="n">
-        <v>298</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4087</v>
+        <v>3.052</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.4969</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9141</v>
+        <v>0.7398</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4087</v>
+        <v>3.052</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4087</v>
+        <v>3.052</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4087</v>
+        <v>3.3419</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7379</v>
+        <v>4.6134</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>298</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7379</v>
+        <v>4.6134</v>
       </c>
       <c r="N8" t="n">
-        <v>394</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7568</v>
+        <v>2.8674</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4488</v>
+        <v>0.4668</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6544</v>
+        <v>0.6565</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7568</v>
+        <v>2.8674</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7568</v>
+        <v>2.8674</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7568</v>
+        <v>2.9366</v>
       </c>
       <c r="I9" t="n">
-        <v>3.023</v>
+        <v>3.314</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.023</v>
+        <v>3.314</v>
       </c>
       <c r="N9" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>ZOREE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1669</v>
+        <v>2.4634</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3528</v>
+        <v>0.401</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4194</v>
+        <v>0.4741</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1669</v>
+        <v>2.4634</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1669</v>
+        <v>2.4634</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1669</v>
+        <v>2.4634</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2408</v>
+        <v>2.8944</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2408</v>
+        <v>2.8944</v>
       </c>
       <c r="N10" t="n">
         <v>252</v>
@@ -906,124 +906,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1147</v>
+        <v>2.3879</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3443</v>
+        <v>0.3888</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3986</v>
+        <v>0.44</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1147</v>
+        <v>2.3879</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1147</v>
+        <v>2.3879</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1147</v>
+        <v>2.3879</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1686</v>
+        <v>3.7201</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1686</v>
+        <v>3.7201</v>
       </c>
       <c r="N11" t="n">
-        <v>166</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8308</v>
+        <v>2.3318</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2981</v>
+        <v>0.3796</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2855</v>
+        <v>0.4147</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8308</v>
+        <v>2.3318</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8308</v>
+        <v>2.3318</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8308</v>
+        <v>2.3318</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8462</v>
+        <v>2.7397</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8462</v>
+        <v>2.7397</v>
       </c>
       <c r="N12" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>KENSI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7829</v>
+        <v>2.2561</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2903</v>
+        <v>0.3673</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2664</v>
+        <v>0.3805</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7829</v>
+        <v>2.2561</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7829</v>
+        <v>2.2561</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7829</v>
+        <v>2.2561</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8592</v>
+        <v>2.7598</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8592</v>
+        <v>2.7598</v>
       </c>
       <c r="N13" t="n">
         <v>297</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6808</v>
+        <v>1.926</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2736</v>
+        <v>0.3136</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2257</v>
+        <v>0.2315</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6808</v>
+        <v>1.926</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6808</v>
+        <v>1.926</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6808</v>
+        <v>1.926</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7974</v>
+        <v>2.0052</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7974</v>
+        <v>2.0052</v>
       </c>
       <c r="N14" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KENSI</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.655</v>
+        <v>1.8258</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2694</v>
+        <v>0.2972</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2154</v>
+        <v>0.1862</v>
       </c>
       <c r="E15" t="n">
-        <v>1.655</v>
+        <v>1.8258</v>
       </c>
       <c r="F15" t="n">
-        <v>1.655</v>
+        <v>1.8258</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.655</v>
+        <v>1.8258</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7258</v>
+        <v>2.5205</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7258</v>
+        <v>2.5205</v>
       </c>
       <c r="N15" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5562</v>
+        <v>1.76</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2533</v>
+        <v>0.2865</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1761</v>
+        <v>0.1565</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5562</v>
+        <v>1.76</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5562</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5562</v>
+        <v>1.76</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5958</v>
+        <v>2.1529</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5958</v>
+        <v>2.1529</v>
       </c>
       <c r="N16" t="n">
-        <v>198</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3347</v>
+        <v>1.6495</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2173</v>
+        <v>0.2685</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0878</v>
+        <v>0.1067</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3347</v>
+        <v>1.6495</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3347</v>
+        <v>1.6495</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3347</v>
+        <v>1.6495</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3686</v>
+        <v>1.8615</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3686</v>
+        <v>1.8615</v>
       </c>
       <c r="N17" t="n">
         <v>166</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3059</v>
+        <v>1.5119</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2126</v>
+        <v>0.2461</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0764</v>
+        <v>0.0445</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3059</v>
+        <v>1.5119</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3059</v>
+        <v>1.5119</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3059</v>
+        <v>1.5119</v>
       </c>
       <c r="I18" t="n">
-        <v>1.432</v>
+        <v>1.7062</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.432</v>
+        <v>1.7062</v>
       </c>
       <c r="N18" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1681</v>
+        <v>0.2183</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0324</v>
+        <v>-0.0326</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0328</v>
+        <v>1.341</v>
       </c>
       <c r="N19" t="n">
         <v>103</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9237</v>
+        <v>1.175</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1504</v>
+        <v>0.1913</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0759</v>
+        <v>-0.1076</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9237</v>
+        <v>1.175</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9237</v>
+        <v>1.175</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9237</v>
+        <v>1.175</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9472</v>
+        <v>1.326</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9472</v>
+        <v>1.326</v>
       </c>
       <c r="N20" t="n">
         <v>166</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7089</v>
+        <v>1.0118</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1154</v>
+        <v>0.1647</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1615</v>
+        <v>-0.1812</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7089</v>
+        <v>1.0118</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7089</v>
+        <v>1.0118</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7089</v>
+        <v>1.0118</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7149</v>
+        <v>1.5763</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7149</v>
+        <v>1.5763</v>
       </c>
       <c r="N21" t="n">
-        <v>162</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6849</v>
+        <v>0.9827</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1115</v>
+        <v>0.16</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.171</v>
+        <v>-0.1944</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6849</v>
+        <v>0.9827</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6849</v>
+        <v>0.9827</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6849</v>
+        <v>0.9827</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7023</v>
+        <v>1.109</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7023</v>
+        <v>1.109</v>
       </c>
       <c r="N22" t="n">
         <v>198</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6781</v>
+        <v>0.8625</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1104</v>
+        <v>0.1404</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1738</v>
+        <v>-0.2486</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6781</v>
+        <v>0.8625</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6781</v>
+        <v>0.8625</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6781</v>
+        <v>0.8625</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6954</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6954</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>198</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZOREE</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5864</v>
+        <v>0.7258</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0955</v>
+        <v>0.1182</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2103</v>
+        <v>-0.3104</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5864</v>
+        <v>0.7258</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5864</v>
+        <v>0.7258</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5864</v>
+        <v>0.7258</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.7557</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.7557</v>
       </c>
       <c r="N24" t="n">
-        <v>252</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1046</v>
+        <v>0.5874</v>
       </c>
       <c r="C25" t="n">
-        <v>0.017</v>
+        <v>0.0956</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4022</v>
+        <v>-0.3728</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1046</v>
+        <v>0.5874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1046</v>
+        <v>0.5874</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1046</v>
+        <v>0.5874</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1055</v>
+        <v>0.6116</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1055</v>
+        <v>0.6116</v>
       </c>
       <c r="N25" t="n">
         <v>162</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0565</v>
+        <v>0.5345</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0092</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4664</v>
+        <v>-0.3967</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0565</v>
+        <v>0.5345</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0565</v>
+        <v>0.5345</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0565</v>
+        <v>0.5345</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0579</v>
+        <v>0.6032</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0579</v>
+        <v>0.6032</v>
       </c>
       <c r="N26" t="n">
         <v>166</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.468</v>
+        <v>0.0603</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0762</v>
+        <v>0.0098</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6304</v>
+        <v>-0.6108</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.468</v>
+        <v>0.0603</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.468</v>
+        <v>0.0603</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.468</v>
+        <v>0.0603</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.484</v>
+        <v>0.0709</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.484</v>
+        <v>0.0709</v>
       </c>
       <c r="N27" t="n">
         <v>252</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5343</v>
+        <v>0.0558</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6128</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5343</v>
+        <v>0.0558</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5343</v>
+        <v>0.0558</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5343</v>
+        <v>0.0558</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5713</v>
+        <v>0.077</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5713</v>
+        <v>0.077</v>
       </c>
       <c r="N28" t="n">
         <v>298</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5849</v>
+        <v>-0.1308</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0213</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5849</v>
+        <v>-0.1308</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5849</v>
+        <v>-0.1308</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5849</v>
+        <v>-0.1308</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5998</v>
+        <v>-0.1476</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5998</v>
+        <v>-0.1476</v>
       </c>
       <c r="N29" t="n">
         <v>198</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6341</v>
+        <v>-0.2294</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1032</v>
+        <v>-0.0373</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6965</v>
+        <v>-0.7416</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6341</v>
+        <v>-0.2294</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6341</v>
+        <v>-0.2294</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6341</v>
+        <v>-0.2294</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6341</v>
+        <v>-0.3574</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6341</v>
+        <v>-0.3574</v>
       </c>
       <c r="N30" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1198</v>
+        <v>-0.0516</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7372</v>
+        <v>-0.781</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7361</v>
+        <v>-0.3167</v>
       </c>
       <c r="N31" t="n">
         <v>103</v>
@@ -1872,231 +1872,231 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8953</v>
+        <v>-0.3843</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1458</v>
+        <v>-0.0626</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8006</v>
+        <v>-0.8115</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8953</v>
+        <v>-0.3843</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8953</v>
+        <v>-0.3843</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8953</v>
+        <v>-0.3843</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9818</v>
+        <v>-0.3843</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>394</v>
+        <v>103</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9818</v>
+        <v>-0.3843</v>
       </c>
       <c r="N32" t="n">
-        <v>394</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.033</v>
+        <v>-0.4013</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1682</v>
+        <v>-0.0653</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8555</v>
+        <v>-0.8192</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.033</v>
+        <v>-0.4013</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.033</v>
+        <v>-0.4013</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.033</v>
+        <v>-0.4013</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.033</v>
+        <v>-0.4715</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.033</v>
+        <v>-0.4715</v>
       </c>
       <c r="N33" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.079</v>
+        <v>-0.5653</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1757</v>
+        <v>-0.092</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8738</v>
+        <v>-0.8932</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.079</v>
+        <v>-0.5653</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.079</v>
+        <v>-0.5653</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.079</v>
+        <v>-0.5653</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0881</v>
+        <v>-0.5653</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0881</v>
+        <v>-0.5653</v>
       </c>
       <c r="N34" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1131</v>
+        <v>-0.5669</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1812</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8874</v>
+        <v>-0.8939</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1131</v>
+        <v>-0.5669</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1131</v>
+        <v>-0.5669</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1131</v>
+        <v>-0.5669</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1511</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1511</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>252</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>jemi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.4119</v>
+        <v>-0.7816</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2299</v>
+        <v>-0.1272</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0064</v>
+        <v>-0.9909</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4119</v>
+        <v>-0.7816</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.4119</v>
+        <v>-0.7816</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.4119</v>
+        <v>-0.7816</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.4119</v>
+        <v>-0.9183</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.4119</v>
+        <v>-0.9183</v>
       </c>
       <c r="N36" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6021</v>
+        <v>-0.9581</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2608</v>
+        <v>-0.156</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0822</v>
+        <v>-1.0705</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6021</v>
+        <v>-0.9581</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6021</v>
+        <v>-0.9581</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6021</v>
+        <v>-0.9581</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6156</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6156</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>162</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>jemi</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7527</v>
+        <v>-1.0374</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2853</v>
+        <v>-0.1689</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1422</v>
+        <v>-1.1063</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7527</v>
+        <v>-1.0374</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7527</v>
+        <v>-1.0374</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7527</v>
+        <v>-1.0374</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8125</v>
+        <v>-1.0374</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>252</v>
+        <v>103</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.8125</v>
+        <v>-1.0374</v>
       </c>
       <c r="N38" t="n">
-        <v>252</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7936</v>
+        <v>-1.1564</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.292</v>
+        <v>-0.1883</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1585</v>
+        <v>-1.1601</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7936</v>
+        <v>-1.1564</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7936</v>
+        <v>-1.1564</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7936</v>
+        <v>-1.1564</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8393</v>
+        <v>-1.305</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8393</v>
+        <v>-1.305</v>
       </c>
       <c r="N39" t="n">
         <v>166</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2237</v>
+        <v>-1.3944</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.362</v>
+        <v>-0.227</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3298</v>
+        <v>-1.2675</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2237</v>
+        <v>-1.3944</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2237</v>
+        <v>-1.3944</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2237</v>
+        <v>-1.3944</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3189</v>
+        <v>-1.7057</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3189</v>
+        <v>-1.7057</v>
       </c>
       <c r="N40" t="n">
         <v>297</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3501</v>
+        <v>-1.4527</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3826</v>
+        <v>-0.2365</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3802</v>
+        <v>-1.2938</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3501</v>
+        <v>-1.4527</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3501</v>
+        <v>-1.4527</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3501</v>
+        <v>-1.4527</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4507</v>
+        <v>-1.777</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4507</v>
+        <v>-1.777</v>
       </c>
       <c r="N41" t="n">
         <v>297</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5844</v>
+        <v>0.5067</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5844</v>
+        <v>0.5067</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3428</v>
+        <v>0.2908</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3428</v>
+        <v>0.2908</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1667</v>
+        <v>0.1613</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1667</v>
+        <v>0.1613</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0505</v>
+        <v>-0.0104</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0505</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2577</v>
+        <v>-0.1468</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2577</v>
+        <v>-0.1468</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4227</v>
+        <v>0.49</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4227</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1509</v>
+        <v>0.1597</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1509</v>
+        <v>0.1597</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1187</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1187</v>
+        <v>-0.06419999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1393</v>
+        <v>-0.0769</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1393</v>
+        <v>-0.0769</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3117</v>
+        <v>-0.1891</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3117</v>
+        <v>-0.1891</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4243</v>
+        <v>0.3535</v>
       </c>
       <c r="J12" t="n">
-        <v>12.729</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.353</v>
+        <v>0.2898</v>
       </c>
       <c r="J13" t="n">
-        <v>10.59</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0083</v>
+        <v>0.0227</v>
       </c>
       <c r="J14" t="n">
-        <v>0.249</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1106</v>
+        <v>-0.0545</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.318</v>
+        <v>-1.635</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.82</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3649</v>
+        <v>-0.2241</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.947</v>
+        <v>-6.723</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6492</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>19.476</v>
+        <v>23.997</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3329</v>
+        <v>0.4035</v>
       </c>
       <c r="J18" t="n">
-        <v>9.987</v>
+        <v>12.105</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2686</v>
+        <v>0.3332</v>
       </c>
       <c r="J19" t="n">
-        <v>8.058</v>
+        <v>9.996</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1372</v>
+        <v>0.203</v>
       </c>
       <c r="J20" t="n">
-        <v>4.116</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.383</v>
+        <v>-0.2342</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.49</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4323</v>
+        <v>0.4996</v>
       </c>
       <c r="J22" t="n">
-        <v>12.5367</v>
+        <v>14.4884</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0145</v>
+        <v>0.0022</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4205</v>
+        <v>0.0638</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0556</v>
+        <v>-0.0347</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6124</v>
+        <v>-1.0063</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2558</v>
+        <v>-0.1541</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.4182</v>
+        <v>-4.4689</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3499</v>
+        <v>-0.2167</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.1471</v>
+        <v>-6.2843</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4463</v>
+        <v>0.3894</v>
       </c>
       <c r="J27" t="n">
-        <v>12.9427</v>
+        <v>11.2926</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4326</v>
+        <v>0.3777</v>
       </c>
       <c r="J28" t="n">
-        <v>12.5454</v>
+        <v>10.9533</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3903</v>
+        <v>0.3424</v>
       </c>
       <c r="J29" t="n">
-        <v>11.3187</v>
+        <v>9.929600000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1897</v>
+        <v>0.195</v>
       </c>
       <c r="J30" t="n">
-        <v>5.5013</v>
+        <v>5.655</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.98</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1256</v>
+        <v>-0.0543</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.6424</v>
+        <v>-1.5747</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.26</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4611</v>
+        <v>0.5406</v>
       </c>
       <c r="J32" t="n">
-        <v>13.833</v>
+        <v>16.218</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1853</v>
+        <v>0.201</v>
       </c>
       <c r="J33" t="n">
-        <v>5.559</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0376</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.304</v>
+        <v>-1.128</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1219</v>
+        <v>-0.065</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.657</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3733</v>
+        <v>-0.231</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.199</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.66</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8912</v>
+        <v>0.8071</v>
       </c>
       <c r="J37" t="n">
-        <v>26.736</v>
+        <v>24.213</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4144</v>
+        <v>0.358</v>
       </c>
       <c r="J38" t="n">
-        <v>12.432</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0961</v>
+        <v>0.1132</v>
       </c>
       <c r="J39" t="n">
-        <v>2.883</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0978</v>
       </c>
       <c r="J40" t="n">
-        <v>2.334</v>
+        <v>2.934</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4932</v>
+        <v>-0.3143</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.796</v>
+        <v>-9.429</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8627</v>
+        <v>0.8319</v>
       </c>
       <c r="J42" t="n">
-        <v>24.1556</v>
+        <v>23.2932</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6469</v>
+        <v>0.6066</v>
       </c>
       <c r="J43" t="n">
-        <v>18.1132</v>
+        <v>16.9848</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2222</v>
+        <v>-0.1731</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.2216</v>
+        <v>-4.8468</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3542</v>
+        <v>-0.2997</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.9176</v>
+        <v>-8.3916</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6805</v>
+        <v>-0.6312</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.054</v>
+        <v>-17.6736</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6959</v>
+        <v>0.8588</v>
       </c>
       <c r="J47" t="n">
-        <v>19.4852</v>
+        <v>24.0464</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1818</v>
+        <v>0.2127</v>
       </c>
       <c r="J48" t="n">
-        <v>5.0904</v>
+        <v>5.9556</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0422</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.6516</v>
+        <v>-1.1816</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2296</v>
+        <v>-0.1303</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.4288</v>
+        <v>-3.6484</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2626</v>
+        <v>-0.1526</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.3528</v>
+        <v>-4.2728</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2247</v>
+        <v>1.1382</v>
       </c>
       <c r="J52" t="n">
-        <v>34.2916</v>
+        <v>31.8696</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8848</v>
+        <v>0.8681</v>
       </c>
       <c r="J53" t="n">
-        <v>24.7744</v>
+        <v>24.3068</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5703</v>
+        <v>0.5533</v>
       </c>
       <c r="J54" t="n">
-        <v>15.9684</v>
+        <v>15.4924</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3906</v>
+        <v>-0.3225</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.9368</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0022</v>
+        <v>-0.9777</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.0616</v>
+        <v>-27.3756</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.214</v>
+        <v>0.2192</v>
       </c>
       <c r="J57" t="n">
-        <v>5.992</v>
+        <v>6.1376</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1581</v>
+        <v>0.1521</v>
       </c>
       <c r="J58" t="n">
-        <v>4.4268</v>
+        <v>4.2588</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0767</v>
+        <v>-0.0591</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.1476</v>
+        <v>-1.6548</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.584</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5097</v>
+        <v>-0.3299</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.2716</v>
+        <v>-9.2372</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2099</v>
+        <v>-0.1832</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.4079</v>
+        <v>-3.8472</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2258</v>
+        <v>-0.194</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.7418</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.62</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.535</v>
+        <v>-0.3664</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.235</v>
+        <v>-7.6944</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.58</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5945</v>
+        <v>-0.4035</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.4845</v>
+        <v>-8.4735</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6229</v>
+        <v>-0.4222</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.0809</v>
+        <v>-8.866199999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.89</v>
       </c>
       <c r="I67" t="n">
-        <v>1.8349</v>
+        <v>1.555</v>
       </c>
       <c r="J67" t="n">
-        <v>38.5329</v>
+        <v>32.655</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.6</v>
       </c>
       <c r="I68" t="n">
-        <v>1.31</v>
+        <v>1.219</v>
       </c>
       <c r="J68" t="n">
-        <v>27.51</v>
+        <v>25.599</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.46</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0186</v>
+        <v>1.0519</v>
       </c>
       <c r="J69" t="n">
-        <v>21.3906</v>
+        <v>22.0899</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6365</v>
+        <v>0.7497</v>
       </c>
       <c r="J70" t="n">
-        <v>13.3665</v>
+        <v>15.7437</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5037</v>
+        <v>-0.4256</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.5777</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4895</v>
+        <v>0.4172</v>
       </c>
       <c r="J72" t="n">
-        <v>13.706</v>
+        <v>11.6816</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4495</v>
+        <v>0.3809</v>
       </c>
       <c r="J73" t="n">
-        <v>12.586</v>
+        <v>10.6652</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3654</v>
+        <v>0.3068</v>
       </c>
       <c r="J74" t="n">
-        <v>10.2312</v>
+        <v>8.590400000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.044</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.232</v>
+        <v>-0.2296</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5481</v>
+        <v>-0.3555</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.3468</v>
+        <v>-9.954000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4227</v>
+        <v>0.3749</v>
       </c>
       <c r="J77" t="n">
-        <v>11.8356</v>
+        <v>10.4972</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3945</v>
+        <v>0.3472</v>
       </c>
       <c r="J78" t="n">
-        <v>11.046</v>
+        <v>9.7216</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0619</v>
+        <v>0.0494</v>
       </c>
       <c r="J79" t="n">
-        <v>1.7332</v>
+        <v>1.3832</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1393</v>
+        <v>-0.0769</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.9004</v>
+        <v>-2.1532</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.64</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5982</v>
+        <v>-0.3935</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.7496</v>
+        <v>-11.018</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4623</v>
+        <v>0.5515</v>
       </c>
       <c r="J82" t="n">
-        <v>16.6428</v>
+        <v>19.854</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4488</v>
+        <v>0.5344</v>
       </c>
       <c r="J83" t="n">
-        <v>16.1568</v>
+        <v>19.2384</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2889</v>
+        <v>0.3407</v>
       </c>
       <c r="J84" t="n">
-        <v>10.4004</v>
+        <v>12.2652</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0375</v>
+        <v>0.078</v>
       </c>
       <c r="J85" t="n">
-        <v>1.35</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4842</v>
+        <v>-0.3083</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.4312</v>
+        <v>-11.0988</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6529</v>
+        <v>0.6107</v>
       </c>
       <c r="J87" t="n">
-        <v>23.5044</v>
+        <v>21.9852</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2513</v>
+        <v>0.2224</v>
       </c>
       <c r="J88" t="n">
-        <v>9.046799999999999</v>
+        <v>8.006399999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2156</v>
+        <v>0.191</v>
       </c>
       <c r="J89" t="n">
-        <v>7.7616</v>
+        <v>6.876</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3489</v>
+        <v>-0.2969</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.5604</v>
+        <v>-10.6884</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4381</v>
+        <v>-0.3845</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.7716</v>
+        <v>-13.842</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.77</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.2485</v>
+        <v>-0.2135</v>
       </c>
       <c r="J92" t="n">
-        <v>-5.2185</v>
+        <v>-4.4835</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3108</v>
+        <v>-0.2555</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.5268</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4792</v>
+        <v>-0.3512</v>
       </c>
       <c r="J94" t="n">
-        <v>-10.0632</v>
+        <v>-7.3752</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.58</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5726</v>
+        <v>-0.3956</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.0246</v>
+        <v>-8.307600000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.43</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7833</v>
+        <v>-0.5364</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.4493</v>
+        <v>-11.2644</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.761</v>
+        <v>1.5064</v>
       </c>
       <c r="J97" t="n">
-        <v>36.981</v>
+        <v>31.6344</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.3617</v>
+        <v>1.2522</v>
       </c>
       <c r="J98" t="n">
-        <v>28.5957</v>
+        <v>26.2962</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0081</v>
+        <v>1.0507</v>
       </c>
       <c r="J99" t="n">
-        <v>21.1701</v>
+        <v>22.0647</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4487</v>
+        <v>0.5593</v>
       </c>
       <c r="J100" t="n">
-        <v>9.422700000000001</v>
+        <v>11.7453</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0674</v>
+        <v>0.159</v>
       </c>
       <c r="J101" t="n">
-        <v>1.4154</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3041</v>
+        <v>0.3289</v>
       </c>
       <c r="J102" t="n">
-        <v>8.210699999999999</v>
+        <v>8.8803</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0056</v>
+        <v>-0.014</v>
       </c>
       <c r="J103" t="n">
-        <v>0.1512</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.8627</v>
+        <v>-3.1212</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1995</v>
+        <v>-0.1266</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.3865</v>
+        <v>-3.4182</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.2921</v>
+        <v>-8.5914</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.783</v>
+        <v>1.5158</v>
       </c>
       <c r="J107" t="n">
-        <v>48.141</v>
+        <v>40.9266</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8356</v>
+        <v>0.8275</v>
       </c>
       <c r="J108" t="n">
-        <v>22.5612</v>
+        <v>22.3425</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1323</v>
+        <v>0.1929</v>
       </c>
       <c r="J109" t="n">
-        <v>3.5721</v>
+        <v>5.2083</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1093</v>
+        <v>-0.0395</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.9511</v>
+        <v>-1.0665</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0336</v>
+        <v>-1.0127</v>
       </c>
       <c r="J111" t="n">
-        <v>-27.9072</v>
+        <v>-27.3429</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3839</v>
+        <v>0.4308</v>
       </c>
       <c r="J112" t="n">
-        <v>13.4365</v>
+        <v>15.078</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3541</v>
+        <v>0.3921</v>
       </c>
       <c r="J113" t="n">
-        <v>12.3935</v>
+        <v>13.7235</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.96</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0612</v>
+        <v>-0.0563</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.142</v>
+        <v>-1.9705</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.49</v>
+        <v>-0.3169</v>
       </c>
       <c r="J115" t="n">
-        <v>-17.15</v>
+        <v>-11.0915</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6575</v>
+        <v>-0.4386</v>
       </c>
       <c r="J116" t="n">
-        <v>-23.0125</v>
+        <v>-15.351</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4809</v>
+        <v>1.3089</v>
       </c>
       <c r="J117" t="n">
-        <v>51.8315</v>
+        <v>45.8115</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3718</v>
+        <v>0.3546</v>
       </c>
       <c r="J118" t="n">
-        <v>13.013</v>
+        <v>12.411</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0382</v>
+        <v>0.0785</v>
       </c>
       <c r="J119" t="n">
-        <v>1.337</v>
+        <v>2.7475</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1702</v>
+        <v>-0.1124</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.957</v>
+        <v>-3.934</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9928</v>
+        <v>-0.9678</v>
       </c>
       <c r="J121" t="n">
-        <v>-34.748</v>
+        <v>-33.873</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2949</v>
+        <v>0.3268</v>
       </c>
       <c r="J122" t="n">
-        <v>10.3215</v>
+        <v>11.438</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.279</v>
+        <v>0.3073</v>
       </c>
       <c r="J123" t="n">
-        <v>9.765000000000001</v>
+        <v>10.7555</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1164</v>
+        <v>0.1168</v>
       </c>
       <c r="J124" t="n">
-        <v>4.074</v>
+        <v>4.088</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.01</v>
       </c>
       <c r="I125" t="n">
-        <v>0.043</v>
+        <v>0.0383</v>
       </c>
       <c r="J125" t="n">
-        <v>1.505</v>
+        <v>1.3405</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5709</v>
+        <v>-0.3734</v>
       </c>
       <c r="J126" t="n">
-        <v>-19.9815</v>
+        <v>-13.069</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0478</v>
+        <v>1.0226</v>
       </c>
       <c r="J127" t="n">
-        <v>36.673</v>
+        <v>35.791</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6841</v>
+        <v>0.67</v>
       </c>
       <c r="J128" t="n">
-        <v>23.9435</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4064</v>
+        <v>0.4222</v>
       </c>
       <c r="J129" t="n">
-        <v>14.224</v>
+        <v>14.777</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.21</v>
+        <v>0.2594</v>
       </c>
       <c r="J130" t="n">
-        <v>7.35</v>
+        <v>9.079000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6404</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-22.414</v>
+        <v>-20.3385</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.73</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9194</v>
+        <v>0.8393</v>
       </c>
       <c r="J132" t="n">
-        <v>22.0656</v>
+        <v>20.1432</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6119</v>
       </c>
       <c r="J133" t="n">
-        <v>16.2936</v>
+        <v>14.6856</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.32</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4275</v>
+        <v>0.4089</v>
       </c>
       <c r="J134" t="n">
-        <v>10.26</v>
+        <v>9.813599999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1068</v>
+        <v>0.1373</v>
       </c>
       <c r="J135" t="n">
-        <v>2.5632</v>
+        <v>3.2952</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1715</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.116</v>
+        <v>-1.9584</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2693</v>
+        <v>0.21</v>
       </c>
       <c r="J137" t="n">
-        <v>6.4632</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2031</v>
+        <v>-0.1735</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.8744</v>
+        <v>-4.164</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3013</v>
+        <v>-0.2352</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.2312</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7309</v>
+        <v>-0.4959</v>
       </c>
       <c r="J140" t="n">
-        <v>-17.5416</v>
+        <v>-11.9016</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.47</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7561</v>
+        <v>-0.5145</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.1464</v>
+        <v>-12.348</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5693</v>
+        <v>0.681</v>
       </c>
       <c r="J142" t="n">
-        <v>13.6632</v>
+        <v>16.344</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0886</v>
+        <v>0.0606</v>
       </c>
       <c r="J143" t="n">
-        <v>2.1264</v>
+        <v>1.4544</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2009</v>
+        <v>-0.1346</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.8216</v>
+        <v>-3.2304</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2746</v>
+        <v>-0.1761</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.5904</v>
+        <v>-4.2264</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8321</v>
+        <v>-0.5722</v>
       </c>
       <c r="J146" t="n">
-        <v>-19.9704</v>
+        <v>-13.7328</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.87</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8592</v>
+        <v>1.5689</v>
       </c>
       <c r="J147" t="n">
-        <v>44.6208</v>
+        <v>37.6536</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.946</v>
       </c>
       <c r="J148" t="n">
-        <v>22.1496</v>
+        <v>22.704</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9003</v>
+        <v>0.9257</v>
       </c>
       <c r="J149" t="n">
-        <v>21.6072</v>
+        <v>22.2168</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2114</v>
+        <v>-0.1259</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.0736</v>
+        <v>-3.0216</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6303</v>
+        <v>-0.5645</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.1272</v>
+        <v>-13.548</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.7424</v>
+        <v>-1.9932</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1134</v>
+        <v>-0.1144</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.4948</v>
+        <v>-2.5168</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5219</v>
+        <v>-0.3535</v>
       </c>
       <c r="J154" t="n">
-        <v>-11.4818</v>
+        <v>-7.777</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.59</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5941</v>
+        <v>-0.4002</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.0702</v>
+        <v>-8.804399999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6622</v>
+        <v>-0.447</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.5684</v>
+        <v>-9.834</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.8</v>
       </c>
       <c r="I157" t="n">
-        <v>1.6835</v>
+        <v>1.4542</v>
       </c>
       <c r="J157" t="n">
-        <v>37.037</v>
+        <v>31.9924</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.77</v>
       </c>
       <c r="I158" t="n">
-        <v>1.6303</v>
+        <v>1.4196</v>
       </c>
       <c r="J158" t="n">
-        <v>35.8666</v>
+        <v>31.2312</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.58</v>
       </c>
       <c r="I159" t="n">
-        <v>1.2755</v>
+        <v>1.1968</v>
       </c>
       <c r="J159" t="n">
-        <v>28.061</v>
+        <v>26.3296</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3121</v>
+        <v>0.4142</v>
       </c>
       <c r="J160" t="n">
-        <v>6.8662</v>
+        <v>9.112399999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.0214</v>
+        <v>-15.8664</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3932</v>
+        <v>1.2503</v>
       </c>
       <c r="J162" t="n">
-        <v>40.4028</v>
+        <v>36.2587</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3409</v>
+        <v>0.2928</v>
       </c>
       <c r="J163" t="n">
-        <v>9.886100000000001</v>
+        <v>8.491199999999999</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4789</v>
+        <v>-0.4312</v>
       </c>
       <c r="J164" t="n">
-        <v>-13.8881</v>
+        <v>-12.5048</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.83</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>-17.0288</v>
+        <v>-15.6542</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.65</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0141</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>-29.4089</v>
+        <v>-28.8086</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.22</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3874</v>
+        <v>0.4539</v>
       </c>
       <c r="J167" t="n">
-        <v>11.2346</v>
+        <v>13.1631</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3874</v>
+        <v>0.4539</v>
       </c>
       <c r="J168" t="n">
-        <v>11.2346</v>
+        <v>13.1631</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3731</v>
+        <v>0.4362</v>
       </c>
       <c r="J169" t="n">
-        <v>10.8199</v>
+        <v>12.6498</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1398</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.0542</v>
+        <v>-2.0445</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.467</v>
+        <v>-0.2962</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.543</v>
+        <v>-8.5898</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2461</v>
+        <v>1.1563</v>
       </c>
       <c r="J172" t="n">
-        <v>36.1369</v>
+        <v>33.5327</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7729</v>
+        <v>0.7726</v>
       </c>
       <c r="J173" t="n">
-        <v>22.4141</v>
+        <v>22.4054</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3264</v>
+        <v>0.3864</v>
       </c>
       <c r="J174" t="n">
-        <v>9.4656</v>
+        <v>11.2056</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0533</v>
+        <v>0.1212</v>
       </c>
       <c r="J175" t="n">
-        <v>1.5457</v>
+        <v>3.5148</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.99</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1789</v>
+        <v>-0.1015</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.1881</v>
+        <v>-2.9435</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2871</v>
+        <v>0.3137</v>
       </c>
       <c r="J177" t="n">
-        <v>8.325900000000001</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0551</v>
+        <v>0.042</v>
       </c>
       <c r="J178" t="n">
-        <v>1.5979</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.019</v>
+        <v>0.0035</v>
       </c>
       <c r="J179" t="n">
-        <v>0.551</v>
+        <v>0.1015</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1235</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.5815</v>
+        <v>-2.1286</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4061</v>
+        <v>-0.2558</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.7769</v>
+        <v>-7.4182</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5677</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>23.8434</v>
+        <v>28.728</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.13</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2586</v>
+        <v>0.294</v>
       </c>
       <c r="J183" t="n">
-        <v>10.8612</v>
+        <v>12.348</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0327</v>
+        <v>0.0597</v>
       </c>
       <c r="J184" t="n">
-        <v>1.3734</v>
+        <v>2.5074</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.112</v>
+        <v>-0.0549</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.704</v>
+        <v>-2.3058</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4224</v>
+        <v>-0.2646</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.7408</v>
+        <v>-11.1132</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2639</v>
+        <v>1.1619</v>
       </c>
       <c r="J187" t="n">
-        <v>53.0838</v>
+        <v>48.7998</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5858</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>24.6036</v>
+        <v>22.6296</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.34</v>
+        <v>-0.2924</v>
       </c>
       <c r="J189" t="n">
-        <v>-14.28</v>
+        <v>-12.2808</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.82</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.62</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>-26.04</v>
+        <v>-23.9862</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9968</v>
+        <v>-0.9738</v>
       </c>
       <c r="J191" t="n">
-        <v>-41.8656</v>
+        <v>-40.8996</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.66</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8727</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>20.9448</v>
+        <v>18.9552</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.55</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.6728</v>
       </c>
       <c r="J193" t="n">
-        <v>18.06</v>
+        <v>16.1472</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0424</v>
+        <v>0.0736</v>
       </c>
       <c r="J194" t="n">
-        <v>1.0176</v>
+        <v>1.7664</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2285</v>
+        <v>-0.1231</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.484</v>
+        <v>-2.9544</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2285</v>
+        <v>-0.1231</v>
       </c>
       <c r="J196" t="n">
-        <v>-5.484</v>
+        <v>-2.9544</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.09</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2941</v>
+        <v>0.2344</v>
       </c>
       <c r="J197" t="n">
-        <v>7.0584</v>
+        <v>5.6256</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1345</v>
+        <v>0.0785</v>
       </c>
       <c r="J198" t="n">
-        <v>3.228</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3878</v>
+        <v>-0.2614</v>
       </c>
       <c r="J199" t="n">
-        <v>-9.3072</v>
+        <v>-6.2736</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.6045</v>
+        <v>-0.403</v>
       </c>
       <c r="J200" t="n">
-        <v>-14.508</v>
+        <v>-9.672000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.49</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.505</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.868</v>
+        <v>-12.12</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.88</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1477</v>
+        <v>-0.1306</v>
       </c>
       <c r="J202" t="n">
-        <v>-3.1017</v>
+        <v>-2.7426</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.84</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.216</v>
+        <v>-0.1737</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.536</v>
+        <v>-3.6477</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2857</v>
+        <v>-0.214</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.9997</v>
+        <v>-4.494</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.73</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.417</v>
+        <v>-0.2795</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.757</v>
+        <v>-5.8695</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5208</v>
+        <v>-0.3458</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9368</v>
+        <v>-7.2618</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.76</v>
       </c>
       <c r="I207" t="n">
-        <v>1.676</v>
+        <v>1.443</v>
       </c>
       <c r="J207" t="n">
-        <v>35.196</v>
+        <v>30.303</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.597</v>
+        <v>0.6652</v>
       </c>
       <c r="J208" t="n">
-        <v>12.537</v>
+        <v>13.9692</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.15</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3388</v>
+        <v>0.4204</v>
       </c>
       <c r="J209" t="n">
-        <v>7.1148</v>
+        <v>8.8284</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2857</v>
+        <v>0.3674</v>
       </c>
       <c r="J210" t="n">
-        <v>5.9997</v>
+        <v>7.7154</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1752</v>
+        <v>0.256</v>
       </c>
       <c r="J211" t="n">
-        <v>3.6792</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.61</v>
       </c>
       <c r="I212" t="n">
-        <v>1.3818</v>
+        <v>1.2521</v>
       </c>
       <c r="J212" t="n">
-        <v>34.545</v>
+        <v>31.3025</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.48</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1249</v>
+        <v>1.0923</v>
       </c>
       <c r="J213" t="n">
-        <v>28.1225</v>
+        <v>27.3075</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.523</v>
+        <v>0.6107</v>
       </c>
       <c r="J214" t="n">
-        <v>13.075</v>
+        <v>15.2675</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4984</v>
+        <v>0.5868</v>
       </c>
       <c r="J215" t="n">
-        <v>12.46</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0914</v>
       </c>
       <c r="J216" t="n">
-        <v>0.24</v>
+        <v>2.285</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.047</v>
+        <v>-0.0626</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.175</v>
+        <v>-1.565</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1024</v>
+        <v>-0.0992</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.56</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1203</v>
+        <v>-0.1109</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.0075</v>
+        <v>-2.7725</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.72</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4393</v>
+        <v>-0.2912</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.9825</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7095</v>
+        <v>-0.4787</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.7375</v>
+        <v>-11.9675</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7651</v>
+        <v>0.7825</v>
       </c>
       <c r="J222" t="n">
-        <v>19.8926</v>
+        <v>20.345</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7405</v>
+        <v>0.7599</v>
       </c>
       <c r="J223" t="n">
-        <v>19.253</v>
+        <v>19.7574</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.598</v>
+        <v>0.6471</v>
       </c>
       <c r="J224" t="n">
-        <v>15.548</v>
+        <v>16.8246</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.21</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5132</v>
+        <v>0.5772</v>
       </c>
       <c r="J225" t="n">
-        <v>13.3432</v>
+        <v>15.0072</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4334</v>
+        <v>0.5039</v>
       </c>
       <c r="J226" t="n">
-        <v>11.2684</v>
+        <v>13.1014</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.334</v>
+        <v>0.361</v>
       </c>
       <c r="J227" t="n">
-        <v>8.683999999999999</v>
+        <v>9.385999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1334</v>
+        <v>0.1066</v>
       </c>
       <c r="J228" t="n">
-        <v>3.4684</v>
+        <v>2.7716</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3682</v>
+        <v>-0.2403</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.5732</v>
+        <v>-6.2478</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4287</v>
+        <v>-0.2792</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.1462</v>
+        <v>-7.2592</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.58</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6449</v>
+        <v>-0.4302</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.7674</v>
+        <v>-11.1852</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.43</v>
       </c>
       <c r="I232" t="n">
-        <v>1.082</v>
+        <v>1.0519</v>
       </c>
       <c r="J232" t="n">
-        <v>28.132</v>
+        <v>27.3494</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9096</v>
+        <v>0.9091</v>
       </c>
       <c r="J233" t="n">
-        <v>23.6496</v>
+        <v>23.6366</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8872</v>
+        <v>0.8868</v>
       </c>
       <c r="J234" t="n">
-        <v>23.0672</v>
+        <v>23.0568</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2392</v>
+        <v>0.3039</v>
       </c>
       <c r="J235" t="n">
-        <v>6.2192</v>
+        <v>7.9014</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8439</v>
+        <v>-0.8004</v>
       </c>
       <c r="J236" t="n">
-        <v>-21.9414</v>
+        <v>-20.8104</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.21</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4191</v>
+        <v>0.4788</v>
       </c>
       <c r="J237" t="n">
-        <v>10.8966</v>
+        <v>12.4488</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.05</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1605</v>
+        <v>0.1537</v>
       </c>
       <c r="J238" t="n">
-        <v>4.173</v>
+        <v>3.9962</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0001</v>
+        <v>-0.0154</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0026</v>
+        <v>-0.4004</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4679</v>
+        <v>-0.3005</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.1654</v>
+        <v>-7.813</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4815</v>
+        <v>-0.3101</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.519</v>
+        <v>-8.0626</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2655</v>
+        <v>0.2281</v>
       </c>
       <c r="J242" t="n">
-        <v>6.6375</v>
+        <v>5.7025</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.09</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1975</v>
+        <v>0.1674</v>
       </c>
       <c r="J243" t="n">
-        <v>4.9375</v>
+        <v>4.185</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1792</v>
+        <v>0.1516</v>
       </c>
       <c r="J244" t="n">
-        <v>4.48</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0389</v>
       </c>
       <c r="J245" t="n">
-        <v>-2.065</v>
+        <v>-0.9725</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.88</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2702</v>
+        <v>-0.1597</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.755</v>
+        <v>-3.9925</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7444</v>
+        <v>0.6609</v>
       </c>
       <c r="J247" t="n">
-        <v>18.61</v>
+        <v>16.5225</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3051</v>
+        <v>0.2633</v>
       </c>
       <c r="J248" t="n">
-        <v>7.6275</v>
+        <v>6.5825</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2726</v>
+        <v>0.2381</v>
       </c>
       <c r="J249" t="n">
-        <v>6.815</v>
+        <v>5.9525</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0213</v>
+        <v>0.0116</v>
       </c>
       <c r="J250" t="n">
-        <v>-0.5325</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4096</v>
+        <v>-0.2535</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.24</v>
+        <v>-6.3375</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.46</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2164</v>
+        <v>1.1307</v>
       </c>
       <c r="J252" t="n">
-        <v>36.492</v>
+        <v>33.921</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.12</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4169</v>
+        <v>0.3872</v>
       </c>
       <c r="J253" t="n">
-        <v>12.507</v>
+        <v>11.616</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0071</v>
+        <v>0.0427</v>
       </c>
       <c r="J254" t="n">
-        <v>0.213</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3024</v>
+        <v>-0.2443</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.071999999999999</v>
+        <v>-7.329</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8078</v>
+        <v>-0.7654</v>
       </c>
       <c r="J256" t="n">
-        <v>-24.234</v>
+        <v>-22.962</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.6</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8419</v>
+        <v>1.0357</v>
       </c>
       <c r="J257" t="n">
-        <v>25.257</v>
+        <v>31.071</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1145</v>
+        <v>0.1674</v>
       </c>
       <c r="J258" t="n">
-        <v>3.435</v>
+        <v>5.022</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1145</v>
+        <v>0.1674</v>
       </c>
       <c r="J259" t="n">
-        <v>3.435</v>
+        <v>5.022</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1684</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.052</v>
+        <v>-2.607</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3478</v>
+        <v>-0.2101</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.434</v>
+        <v>-6.303</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.86</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1614</v>
+        <v>-0.1443</v>
       </c>
       <c r="J262" t="n">
-        <v>-4.035</v>
+        <v>-3.6075</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.82</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.2276</v>
+        <v>-0.1873</v>
       </c>
       <c r="J263" t="n">
-        <v>-5.69</v>
+        <v>-4.6825</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3111</v>
+        <v>-0.2376</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.7775</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.63</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5486</v>
+        <v>-0.3676</v>
       </c>
       <c r="J265" t="n">
-        <v>-13.715</v>
+        <v>-9.19</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.62</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5627</v>
+        <v>-0.3769</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.0675</v>
+        <v>-9.422499999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.88</v>
       </c>
       <c r="I267" t="n">
-        <v>1.8554</v>
+        <v>1.5667</v>
       </c>
       <c r="J267" t="n">
-        <v>46.385</v>
+        <v>39.1675</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0711</v>
+        <v>1.0635</v>
       </c>
       <c r="J268" t="n">
-        <v>26.7775</v>
+        <v>26.5875</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.34</v>
       </c>
       <c r="I269" t="n">
-        <v>0.7886</v>
+        <v>0.8537</v>
       </c>
       <c r="J269" t="n">
-        <v>19.715</v>
+        <v>21.3425</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.04</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0026</v>
+        <v>0.0859</v>
       </c>
       <c r="J270" t="n">
-        <v>0.065</v>
+        <v>2.1475</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.98</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2654</v>
+        <v>-0.1779</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.635</v>
+        <v>-4.4475</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.49</v>
       </c>
       <c r="I272" t="n">
-        <v>0.854</v>
+        <v>1.0709</v>
       </c>
       <c r="J272" t="n">
-        <v>17.08</v>
+        <v>21.418</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.63</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.5514</v>
+        <v>-0.3688</v>
       </c>
       <c r="J273" t="n">
-        <v>-11.028</v>
+        <v>-7.376</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.58</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.62</v>
+        <v>-0.4156</v>
       </c>
       <c r="J274" t="n">
-        <v>-12.4</v>
+        <v>-8.311999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.58</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.62</v>
+        <v>-0.4156</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.4</v>
+        <v>-8.311999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7736</v>
+        <v>-0.5272</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.472</v>
+        <v>-10.544</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.58</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3187</v>
+        <v>1.2132</v>
       </c>
       <c r="J277" t="n">
-        <v>26.374</v>
+        <v>24.264</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.49</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1395</v>
+        <v>1.1027</v>
       </c>
       <c r="J278" t="n">
-        <v>22.79</v>
+        <v>22.054</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.37</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8782</v>
+        <v>0.9185</v>
       </c>
       <c r="J279" t="n">
-        <v>17.564</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.31</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7148</v>
+        <v>0.7912</v>
       </c>
       <c r="J280" t="n">
-        <v>14.296</v>
+        <v>15.824</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.89</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.536</v>
+        <v>-0.4619</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.72</v>
+        <v>-9.238</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0508</v>
       </c>
       <c r="J282" t="n">
-        <v>1.9558</v>
+        <v>1.1176</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0544</v>
+        <v>0.0108</v>
       </c>
       <c r="J283" t="n">
-        <v>1.1968</v>
+        <v>0.2376</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0346</v>
+        <v>-0.0529</v>
       </c>
       <c r="J284" t="n">
-        <v>-0.7612</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6499</v>
+        <v>-0.4346</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.2978</v>
+        <v>-9.561199999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6626</v>
+        <v>-0.4439</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.5772</v>
+        <v>-9.7658</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.77</v>
       </c>
       <c r="I287" t="n">
-        <v>1.6395</v>
+        <v>1.4242</v>
       </c>
       <c r="J287" t="n">
-        <v>36.069</v>
+        <v>31.3324</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1242</v>
+        <v>1.1041</v>
       </c>
       <c r="J288" t="n">
-        <v>24.7324</v>
+        <v>24.2902</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.44</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9939</v>
+        <v>1.0289</v>
       </c>
       <c r="J289" t="n">
-        <v>21.8658</v>
+        <v>22.6358</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.8371</v>
+        <v>0.929</v>
       </c>
       <c r="J290" t="n">
-        <v>18.4162</v>
+        <v>20.438</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4975</v>
+        <v>-0.4192</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.945</v>
+        <v>-9.2224</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.37</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5555</v>
+        <v>0.4844</v>
       </c>
       <c r="J292" t="n">
-        <v>14.443</v>
+        <v>12.5944</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.21</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3369</v>
+        <v>0.2963</v>
       </c>
       <c r="J293" t="n">
-        <v>8.759399999999999</v>
+        <v>7.7038</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2879</v>
+        <v>0.2597</v>
       </c>
       <c r="J294" t="n">
-        <v>7.4854</v>
+        <v>6.7522</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2296</v>
+        <v>0.2227</v>
       </c>
       <c r="J295" t="n">
-        <v>5.9696</v>
+        <v>5.7902</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2011</v>
+        <v>-0.1058</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.2286</v>
+        <v>-2.7508</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2074</v>
+        <v>0.1531</v>
       </c>
       <c r="J297" t="n">
-        <v>5.3924</v>
+        <v>3.9806</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0793</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.0618</v>
+        <v>-1.9578</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.137</v>
+        <v>-0.1106</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.562</v>
+        <v>-2.8756</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.156</v>
+        <v>-0.1217</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.056</v>
+        <v>-3.1642</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.54</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6983</v>
+        <v>-0.4696</v>
       </c>
       <c r="J301" t="n">
-        <v>-18.1558</v>
+        <v>-12.2096</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.28</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5271</v>
+        <v>0.6227</v>
       </c>
       <c r="J302" t="n">
-        <v>12.6504</v>
+        <v>14.9448</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.98</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0102</v>
+        <v>-0.0269</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.2448</v>
+        <v>-0.6456</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3109</v>
+        <v>-0.1974</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.4616</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3109</v>
+        <v>-0.1974</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.4616</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.61</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.618</v>
+        <v>-0.4095</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.832</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.46</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1624</v>
+        <v>1.1003</v>
       </c>
       <c r="J307" t="n">
-        <v>27.8976</v>
+        <v>26.4072</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5675</v>
       </c>
       <c r="J308" t="n">
-        <v>13.632</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.17</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4824</v>
+        <v>0.4939</v>
       </c>
       <c r="J309" t="n">
-        <v>11.5776</v>
+        <v>11.8536</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1025</v>
+        <v>0.1627</v>
       </c>
       <c r="J310" t="n">
-        <v>2.46</v>
+        <v>3.9048</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.91</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4349</v>
+        <v>-0.3635</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.4376</v>
+        <v>-8.724</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.54</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2328</v>
+        <v>1.1614</v>
       </c>
       <c r="J312" t="n">
-        <v>25.8888</v>
+        <v>24.3894</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.47</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0901</v>
+        <v>1.0754</v>
       </c>
       <c r="J313" t="n">
-        <v>22.8921</v>
+        <v>22.5834</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.35</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8152</v>
+        <v>0.8741</v>
       </c>
       <c r="J314" t="n">
-        <v>17.1192</v>
+        <v>18.3561</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.23</v>
       </c>
       <c r="I315" t="n">
-        <v>0.51</v>
+        <v>0.6049</v>
       </c>
       <c r="J315" t="n">
-        <v>10.71</v>
+        <v>12.7029</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.13</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2604</v>
+        <v>0.352</v>
       </c>
       <c r="J316" t="n">
-        <v>5.4684</v>
+        <v>7.392</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3452</v>
+        <v>0.3746</v>
       </c>
       <c r="J317" t="n">
-        <v>7.2492</v>
+        <v>7.8666</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0673</v>
+        <v>0.0238</v>
       </c>
       <c r="J318" t="n">
-        <v>1.4133</v>
+        <v>0.4998</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0408</v>
+        <v>-0.0596</v>
       </c>
       <c r="J319" t="n">
-        <v>-0.8568</v>
+        <v>-1.2516</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.44</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.8044</v>
+        <v>-0.5505</v>
       </c>
       <c r="J320" t="n">
-        <v>-16.8924</v>
+        <v>-11.5605</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.43</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8163</v>
+        <v>-0.5596</v>
       </c>
       <c r="J321" t="n">
-        <v>-17.1423</v>
+        <v>-11.7516</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.54</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3203</v>
+        <v>1.2028</v>
       </c>
       <c r="J322" t="n">
-        <v>34.3278</v>
+        <v>31.2728</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.45</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1398</v>
+        <v>1.0861</v>
       </c>
       <c r="J323" t="n">
-        <v>29.6348</v>
+        <v>28.2386</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.04</v>
       </c>
       <c r="I324" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="J324" t="n">
-        <v>1.7316</v>
+        <v>3.3462</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1085</v>
+        <v>-0.0389</v>
       </c>
       <c r="J325" t="n">
-        <v>-2.821</v>
+        <v>-1.0114</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7675</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J326" t="n">
-        <v>-19.955</v>
+        <v>-18.6472</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1669</v>
+        <v>0.1584</v>
       </c>
       <c r="J327" t="n">
-        <v>4.3394</v>
+        <v>4.1184</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1295</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.367</v>
+        <v>-2.4258</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.91</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.6202</v>
+        <v>-2.9978</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2516</v>
+        <v>-0.1582</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.5416</v>
+        <v>-4.1132</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.86</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2686</v>
+        <v>-0.1687</v>
       </c>
       <c r="J331" t="n">
-        <v>-6.9836</v>
+        <v>-4.3862</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.3</v>
       </c>
       <c r="I332" t="n">
-        <v>0.5475</v>
+        <v>0.6509</v>
       </c>
       <c r="J332" t="n">
-        <v>14.7825</v>
+        <v>17.5743</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2904</v>
+        <v>0.3108</v>
       </c>
       <c r="J333" t="n">
-        <v>7.8408</v>
+        <v>8.3916</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2053</v>
+        <v>0.2047</v>
       </c>
       <c r="J334" t="n">
-        <v>5.5431</v>
+        <v>5.5269</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.5311</v>
+        <v>-0.346</v>
       </c>
       <c r="J335" t="n">
-        <v>-14.3397</v>
+        <v>-9.342000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8235</v>
+        <v>-0.5656</v>
       </c>
       <c r="J336" t="n">
-        <v>-22.2345</v>
+        <v>-15.2712</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.82</v>
       </c>
       <c r="I337" t="n">
-        <v>1.8528</v>
+        <v>1.5671</v>
       </c>
       <c r="J337" t="n">
-        <v>50.0256</v>
+        <v>42.3117</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.12</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3446</v>
+        <v>0.3724</v>
       </c>
       <c r="J338" t="n">
-        <v>9.3042</v>
+        <v>10.0548</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2481</v>
+        <v>0.2905</v>
       </c>
       <c r="J339" t="n">
-        <v>6.6987</v>
+        <v>7.8435</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.86</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5609</v>
+        <v>-0.4975</v>
       </c>
       <c r="J340" t="n">
-        <v>-15.1443</v>
+        <v>-13.4325</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.75</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.828</v>
+        <v>-0.7845</v>
       </c>
       <c r="J341" t="n">
-        <v>-22.356</v>
+        <v>-21.1815</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4666</v>
+        <v>0.5502</v>
       </c>
       <c r="J342" t="n">
-        <v>22.3968</v>
+        <v>26.4096</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.21</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3834</v>
+        <v>0.4442</v>
       </c>
       <c r="J343" t="n">
-        <v>18.4032</v>
+        <v>21.3216</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0101</v>
+        <v>0.0325</v>
       </c>
       <c r="J344" t="n">
-        <v>0.4848</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2232</v>
+        <v>-0.1277</v>
       </c>
       <c r="J345" t="n">
-        <v>-10.7136</v>
+        <v>-6.1296</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3785</v>
+        <v>-0.2338</v>
       </c>
       <c r="J346" t="n">
-        <v>-18.168</v>
+        <v>-11.2224</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7912</v>
+        <v>0.7637</v>
       </c>
       <c r="J347" t="n">
-        <v>37.9776</v>
+        <v>36.6576</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7393</v>
       </c>
       <c r="J348" t="n">
-        <v>36.8448</v>
+        <v>35.4864</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.22</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6706</v>
+        <v>0.6405</v>
       </c>
       <c r="J349" t="n">
-        <v>32.1888</v>
+        <v>30.744</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5698</v>
+        <v>-0.5111</v>
       </c>
       <c r="J350" t="n">
-        <v>-27.3504</v>
+        <v>-24.5328</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7199</v>
+        <v>-0.6696</v>
       </c>
       <c r="J351" t="n">
-        <v>-34.5552</v>
+        <v>-32.1408</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5454/event_5454_evp_summary.xlsx
+++ b/database/event/5454/event_5454_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5505</v>
+        <v>3.4851</v>
       </c>
       <c r="C2" t="n">
-        <v>0.578</v>
+        <v>0.5674</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9649</v>
+        <v>0.9623</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5505</v>
+        <v>3.4851</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5505</v>
+        <v>3.4851</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4365</v>
+        <v>4.9029</v>
       </c>
       <c r="I2" t="n">
-        <v>6.1245</v>
+        <v>6.0096</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1245</v>
+        <v>6.0096</v>
       </c>
       <c r="N2" t="n">
         <v>298</v>
@@ -538,47 +538,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3524</v>
+        <v>3.2514</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5458</v>
+        <v>0.5293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8754</v>
+        <v>0.8559</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3524</v>
+        <v>3.2514</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3524</v>
+        <v>3.2514</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0014</v>
+        <v>4.3913</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5157</v>
+        <v>5.8095</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5157</v>
+        <v>5.8095</v>
       </c>
       <c r="N3" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3311</v>
+        <v>3.2065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5423</v>
+        <v>0.522</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8658</v>
+        <v>0.8355</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3311</v>
+        <v>3.2065</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3311</v>
+        <v>3.2065</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9547</v>
+        <v>4.293</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4594</v>
+        <v>5.2621</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4594</v>
+        <v>5.2621</v>
       </c>
       <c r="N4" t="n">
         <v>298</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2967</v>
+        <v>3.1145</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5367</v>
+        <v>0.507</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.7936</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2967</v>
+        <v>3.1145</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2967</v>
+        <v>3.1145</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8792</v>
+        <v>4.0918</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7452</v>
+        <v>4.6469</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7452</v>
+        <v>4.6469</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.292</v>
+        <v>3.0991</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5359</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8482</v>
+        <v>0.7866</v>
       </c>
       <c r="E6" t="n">
-        <v>3.292</v>
+        <v>3.0991</v>
       </c>
       <c r="F6" t="n">
-        <v>3.292</v>
+        <v>3.0991</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.869</v>
+        <v>4.058</v>
       </c>
       <c r="I6" t="n">
-        <v>6.0275</v>
+        <v>4.3799</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0275</v>
+        <v>4.3799</v>
       </c>
       <c r="N6" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.057</v>
+        <v>3.029</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4977</v>
+        <v>0.4931</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7421</v>
+        <v>0.7547</v>
       </c>
       <c r="E7" t="n">
-        <v>3.057</v>
+        <v>3.029</v>
       </c>
       <c r="F7" t="n">
-        <v>3.057</v>
+        <v>3.029</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3529</v>
+        <v>3.9046</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2235</v>
+        <v>5.1656</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2235</v>
+        <v>5.1656</v>
       </c>
       <c r="N7" t="n">
         <v>394</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.052</v>
+        <v>2.9183</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4969</v>
+        <v>0.4751</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7398</v>
+        <v>0.7043</v>
       </c>
       <c r="E8" t="n">
-        <v>3.052</v>
+        <v>2.9183</v>
       </c>
       <c r="F8" t="n">
-        <v>3.052</v>
+        <v>2.9183</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3419</v>
+        <v>3.6623</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6134</v>
+        <v>4.489</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6134</v>
+        <v>4.489</v>
       </c>
       <c r="N8" t="n">
         <v>298</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8674</v>
+        <v>2.6174</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4668</v>
+        <v>0.4261</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6565</v>
+        <v>0.5673</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8674</v>
+        <v>2.6174</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8674</v>
+        <v>2.6174</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9366</v>
+        <v>3.0038</v>
       </c>
       <c r="I9" t="n">
-        <v>3.314</v>
+        <v>3.2421</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.314</v>
+        <v>3.2421</v>
       </c>
       <c r="N9" t="n">
         <v>166</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZOREE</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4634</v>
+        <v>2.5112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.401</v>
+        <v>0.4088</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4741</v>
+        <v>0.5189</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4634</v>
+        <v>2.5112</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4634</v>
+        <v>2.5112</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4634</v>
+        <v>2.7712</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8944</v>
+        <v>3.6662</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>252</v>
+        <v>394</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8944</v>
+        <v>3.6662</v>
       </c>
       <c r="N10" t="n">
-        <v>252</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>ZOREE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3879</v>
+        <v>2.3909</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3888</v>
+        <v>0.3892</v>
       </c>
       <c r="D11" t="n">
-        <v>0.44</v>
+        <v>0.4642</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3879</v>
+        <v>2.3909</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3879</v>
+        <v>2.3909</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3879</v>
+        <v>2.5079</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7201</v>
+        <v>2.7766</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>252</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7201</v>
+        <v>2.7766</v>
       </c>
       <c r="N11" t="n">
-        <v>394</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3318</v>
+        <v>2.3342</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3796</v>
+        <v>0.38</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4147</v>
+        <v>0.4384</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3318</v>
+        <v>2.3342</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3318</v>
+        <v>2.3342</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3318</v>
+        <v>2.3838</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7397</v>
+        <v>2.6392</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7397</v>
+        <v>2.6392</v>
       </c>
       <c r="N12" t="n">
         <v>252</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2561</v>
+        <v>2.2569</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3673</v>
+        <v>0.3674</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3805</v>
+        <v>0.4032</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2561</v>
+        <v>2.2569</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2561</v>
+        <v>2.2569</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2561</v>
+        <v>2.2569</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7598</v>
+        <v>2.5631</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7598</v>
+        <v>2.5631</v>
       </c>
       <c r="N13" t="n">
         <v>297</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.926</v>
+        <v>2.0198</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3136</v>
+        <v>0.3288</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2315</v>
+        <v>0.2953</v>
       </c>
       <c r="E14" t="n">
-        <v>1.926</v>
+        <v>2.0198</v>
       </c>
       <c r="F14" t="n">
-        <v>1.926</v>
+        <v>2.0198</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.926</v>
+        <v>2.0198</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0052</v>
+        <v>2.4757</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>298</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0052</v>
+        <v>2.4757</v>
       </c>
       <c r="N14" t="n">
-        <v>162</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8258</v>
+        <v>1.9021</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2972</v>
+        <v>0.3097</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1862</v>
+        <v>0.2417</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8258</v>
+        <v>1.9021</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8258</v>
+        <v>1.9021</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8258</v>
+        <v>1.9021</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5205</v>
+        <v>1.9511</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5205</v>
+        <v>1.9511</v>
       </c>
       <c r="N15" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.76</v>
+        <v>1.8125</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2865</v>
+        <v>0.2951</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1565</v>
+        <v>0.2009</v>
       </c>
       <c r="E16" t="n">
-        <v>1.76</v>
+        <v>1.8125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.76</v>
+        <v>1.8125</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.76</v>
+        <v>1.8125</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1529</v>
+        <v>2.0584</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1529</v>
+        <v>2.0584</v>
       </c>
       <c r="N16" t="n">
         <v>297</v>
@@ -1182,231 +1182,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6495</v>
+        <v>1.5816</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2685</v>
+        <v>0.2575</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1067</v>
+        <v>0.0958</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6495</v>
+        <v>1.5816</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6495</v>
+        <v>1.5816</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6495</v>
+        <v>1.5816</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8615</v>
+        <v>1.707</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8615</v>
+        <v>1.707</v>
       </c>
       <c r="N17" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5119</v>
+        <v>1.5811</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2461</v>
+        <v>0.2574</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0445</v>
+        <v>0.0955</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5119</v>
+        <v>1.5811</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5119</v>
+        <v>1.5811</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5119</v>
+        <v>1.5811</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7062</v>
+        <v>1.7065</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7062</v>
+        <v>1.7065</v>
       </c>
       <c r="N18" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.341</v>
+        <v>1.2611</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2183</v>
+        <v>0.2053</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0326</v>
+        <v>-0.0501</v>
       </c>
       <c r="E19" t="n">
-        <v>1.341</v>
+        <v>1.2611</v>
       </c>
       <c r="F19" t="n">
-        <v>1.341</v>
+        <v>1.2611</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.341</v>
+        <v>1.2611</v>
       </c>
       <c r="I19" t="n">
-        <v>1.341</v>
+        <v>1.6684</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.341</v>
+        <v>1.6684</v>
       </c>
       <c r="N19" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.175</v>
+        <v>1.2583</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1913</v>
+        <v>0.2049</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1076</v>
+        <v>-0.0514</v>
       </c>
       <c r="E20" t="n">
-        <v>1.175</v>
+        <v>1.2583</v>
       </c>
       <c r="F20" t="n">
-        <v>1.175</v>
+        <v>1.2583</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.175</v>
+        <v>1.2583</v>
       </c>
       <c r="I20" t="n">
-        <v>1.326</v>
+        <v>1.2583</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.326</v>
+        <v>1.2583</v>
       </c>
       <c r="N20" t="n">
-        <v>166</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0118</v>
+        <v>1.132</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1647</v>
+        <v>0.1843</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1812</v>
+        <v>-0.1089</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0118</v>
+        <v>1.132</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0118</v>
+        <v>1.132</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0118</v>
+        <v>1.132</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5763</v>
+        <v>1.2218</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5763</v>
+        <v>1.2218</v>
       </c>
       <c r="N21" t="n">
-        <v>394</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9827</v>
+        <v>1.0156</v>
       </c>
       <c r="C22" t="n">
-        <v>0.16</v>
+        <v>0.1653</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1944</v>
+        <v>-0.1619</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9827</v>
+        <v>1.0156</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9827</v>
+        <v>1.0156</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9827</v>
+        <v>1.0156</v>
       </c>
       <c r="I22" t="n">
-        <v>1.109</v>
+        <v>1.0961</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.109</v>
+        <v>1.0961</v>
       </c>
       <c r="N22" t="n">
         <v>198</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8625</v>
+        <v>0.9325</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1404</v>
+        <v>0.1518</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2486</v>
+        <v>-0.1997</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8625</v>
+        <v>0.9325</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8625</v>
+        <v>0.9325</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8625</v>
+        <v>0.9325</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.0065</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.0065</v>
       </c>
       <c r="N23" t="n">
         <v>198</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7258</v>
+        <v>0.7352</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1182</v>
+        <v>0.1197</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3104</v>
+        <v>-0.2895</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7258</v>
+        <v>0.7352</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7258</v>
+        <v>0.7352</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7258</v>
+        <v>0.7352</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7557</v>
+        <v>0.7541</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7557</v>
+        <v>0.7541</v>
       </c>
       <c r="N24" t="n">
         <v>162</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5874</v>
+        <v>0.5592</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0956</v>
+        <v>0.091</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3728</v>
+        <v>-0.3696</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5874</v>
+        <v>0.5592</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5874</v>
+        <v>0.5592</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5874</v>
+        <v>0.5592</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6116</v>
+        <v>0.5736</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6116</v>
+        <v>0.5736</v>
       </c>
       <c r="N25" t="n">
         <v>162</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5345</v>
+        <v>0.4621</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0752</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3967</v>
+        <v>-0.4138</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5345</v>
+        <v>0.4621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5345</v>
+        <v>0.4621</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5345</v>
+        <v>0.4621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6032</v>
+        <v>0.4988</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6032</v>
+        <v>0.4988</v>
       </c>
       <c r="N26" t="n">
         <v>166</v>
@@ -1642,185 +1642,185 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sLowi</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0603</v>
+        <v>0.0653</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0098</v>
+        <v>0.0106</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6108</v>
+        <v>-0.5945</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0603</v>
+        <v>0.0653</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0603</v>
+        <v>0.0653</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0603</v>
+        <v>0.0653</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0709</v>
+        <v>0.0801</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0709</v>
+        <v>0.0801</v>
       </c>
       <c r="N27" t="n">
-        <v>252</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>sLowi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0558</v>
+        <v>-0.0046</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0091</v>
+        <v>-0.0007</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6128</v>
+        <v>-0.6263</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0558</v>
+        <v>-0.0046</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0558</v>
+        <v>-0.0046</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0558</v>
+        <v>-0.0046</v>
       </c>
       <c r="I28" t="n">
-        <v>0.077</v>
+        <v>-0.0051</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.077</v>
+        <v>-0.0051</v>
       </c>
       <c r="N28" t="n">
-        <v>298</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1308</v>
+        <v>-0.1462</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0213</v>
+        <v>-0.0238</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.6908</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1308</v>
+        <v>-0.1462</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1308</v>
+        <v>-0.1462</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1308</v>
+        <v>-0.1462</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1476</v>
+        <v>-0.1934</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1476</v>
+        <v>-0.1934</v>
       </c>
       <c r="N29" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2294</v>
+        <v>-0.218</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0373</v>
+        <v>-0.0355</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7416</v>
+        <v>-0.7234</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2294</v>
+        <v>-0.218</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2294</v>
+        <v>-0.218</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2294</v>
+        <v>-0.218</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3574</v>
+        <v>-0.2353</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3574</v>
+        <v>-0.2353</v>
       </c>
       <c r="N30" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0516</v>
+        <v>-0.0583</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.781</v>
+        <v>-0.7872</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3167</v>
+        <v>-0.3581</v>
       </c>
       <c r="N31" t="n">
         <v>103</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0626</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8115</v>
+        <v>-0.8175</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3843</v>
+        <v>-0.4246</v>
       </c>
       <c r="N32" t="n">
         <v>103</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4013</v>
+        <v>-0.4756</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0653</v>
+        <v>-0.0774</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8192</v>
+        <v>-0.8407</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4013</v>
+        <v>-0.4756</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4013</v>
+        <v>-0.4756</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4013</v>
+        <v>-0.4756</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4715</v>
+        <v>-0.5265</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4715</v>
+        <v>-0.5265</v>
       </c>
       <c r="N33" t="n">
         <v>252</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.092</v>
+        <v>-0.0997</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8932</v>
+        <v>-0.9029</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5653</v>
+        <v>-0.6122</v>
       </c>
       <c r="N34" t="n">
         <v>103</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5669</v>
+        <v>-0.6254</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1018</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8939</v>
+        <v>-0.9089</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5669</v>
+        <v>-0.6254</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5669</v>
+        <v>-0.6254</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5669</v>
+        <v>-0.6254</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6415</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6415</v>
       </c>
       <c r="N35" t="n">
         <v>162</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7816</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1272</v>
+        <v>-0.1417</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9909</v>
+        <v>-1.0205</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7816</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7816</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7816</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9183</v>
+        <v>-0.9638</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9183</v>
+        <v>-0.9638</v>
       </c>
       <c r="N36" t="n">
         <v>252</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9581</v>
+        <v>-1.0248</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.156</v>
+        <v>-0.1668</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0705</v>
+        <v>-1.0907</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9581</v>
+        <v>-1.0248</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9581</v>
+        <v>-1.0248</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9581</v>
+        <v>-1.0248</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-1.0512</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-1.0512</v>
       </c>
       <c r="N37" t="n">
         <v>162</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1689</v>
+        <v>-0.1749</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1063</v>
+        <v>-1.1133</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0374</v>
+        <v>-1.0745</v>
       </c>
       <c r="N38" t="n">
         <v>103</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1564</v>
+        <v>-1.1943</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1883</v>
+        <v>-0.1944</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1601</v>
+        <v>-1.1679</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1564</v>
+        <v>-1.1943</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1564</v>
+        <v>-1.1943</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1564</v>
+        <v>-1.1943</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.305</v>
+        <v>-1.289</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.305</v>
+        <v>-1.289</v>
       </c>
       <c r="N39" t="n">
         <v>166</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3944</v>
+        <v>-1.3868</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.227</v>
+        <v>-0.2258</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2675</v>
+        <v>-1.2555</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3944</v>
+        <v>-1.3868</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3944</v>
+        <v>-1.3868</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3944</v>
+        <v>-1.3868</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7057</v>
+        <v>-1.5749</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7057</v>
+        <v>-1.5749</v>
       </c>
       <c r="N40" t="n">
         <v>297</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4527</v>
+        <v>-1.5055</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2365</v>
+        <v>-0.2451</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2938</v>
+        <v>-1.3095</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4527</v>
+        <v>-1.5055</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4527</v>
+        <v>-1.5055</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4527</v>
+        <v>-1.5055</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.777</v>
+        <v>-1.7097</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.777</v>
+        <v>-1.7097</v>
       </c>
       <c r="N41" t="n">
         <v>297</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5067</v>
+        <v>0.5125</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5067</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2908</v>
+        <v>0.3059</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2908</v>
+        <v>0.3059</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1613</v>
+        <v>0.1771</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1613</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0104</v>
+        <v>-0.008</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0104</v>
+        <v>-0.008</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1468</v>
+        <v>-0.1567</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1468</v>
+        <v>-0.1567</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.49</v>
+        <v>0.4817</v>
       </c>
       <c r="J7" t="n">
-        <v>0.49</v>
+        <v>0.4817</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1597</v>
+        <v>0.1687</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1597</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0733</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0733</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0769</v>
+        <v>-0.0868</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0769</v>
+        <v>-0.0868</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1891</v>
+        <v>-0.2024</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1891</v>
+        <v>-0.2024</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3535</v>
+        <v>0.364</v>
       </c>
       <c r="J12" t="n">
-        <v>10.605</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2898</v>
+        <v>0.3023</v>
       </c>
       <c r="J13" t="n">
-        <v>8.694000000000001</v>
+        <v>9.069000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0227</v>
+        <v>0.0291</v>
       </c>
       <c r="J14" t="n">
-        <v>0.681</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0545</v>
+        <v>-0.0616</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.635</v>
+        <v>-1.848</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.82</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2241</v>
+        <v>-0.2365</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.723</v>
+        <v>-7.095</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7705</v>
       </c>
       <c r="J17" t="n">
-        <v>23.997</v>
+        <v>23.115</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4035</v>
+        <v>0.4081</v>
       </c>
       <c r="J18" t="n">
-        <v>12.105</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3332</v>
+        <v>0.3418</v>
       </c>
       <c r="J19" t="n">
-        <v>9.996</v>
+        <v>10.254</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.203</v>
+        <v>0.2164</v>
       </c>
       <c r="J20" t="n">
-        <v>6.09</v>
+        <v>6.492</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2342</v>
+        <v>-0.2444</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.026</v>
+        <v>-7.332</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4996</v>
+        <v>0.4888</v>
       </c>
       <c r="J22" t="n">
-        <v>14.4884</v>
+        <v>14.1752</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0022</v>
+        <v>0.0016</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0638</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0347</v>
+        <v>-0.0418</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0063</v>
+        <v>-1.2122</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1541</v>
+        <v>-0.1677</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.4689</v>
+        <v>-4.8633</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2167</v>
+        <v>-0.2307</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.2843</v>
+        <v>-6.6903</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3894</v>
+        <v>0.4034</v>
       </c>
       <c r="J27" t="n">
-        <v>11.2926</v>
+        <v>11.6986</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3777</v>
+        <v>0.3922</v>
       </c>
       <c r="J28" t="n">
-        <v>10.9533</v>
+        <v>11.3738</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3424</v>
+        <v>0.3581</v>
       </c>
       <c r="J29" t="n">
-        <v>9.929600000000001</v>
+        <v>10.3849</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.195</v>
+        <v>0.2128</v>
       </c>
       <c r="J30" t="n">
-        <v>5.655</v>
+        <v>6.1712</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.98</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0543</v>
+        <v>-0.0569</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.5747</v>
+        <v>-1.6501</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.26</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5406</v>
+        <v>0.5288</v>
       </c>
       <c r="J32" t="n">
-        <v>16.218</v>
+        <v>15.864</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.201</v>
+        <v>0.2096</v>
       </c>
       <c r="J33" t="n">
-        <v>6.03</v>
+        <v>6.288</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0376</v>
+        <v>-0.0439</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.128</v>
+        <v>-1.317</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.065</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.95</v>
+        <v>-2.217</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.231</v>
+        <v>-0.2441</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.93</v>
+        <v>-7.323</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.66</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8071</v>
+        <v>0.7932</v>
       </c>
       <c r="J37" t="n">
-        <v>24.213</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.358</v>
+        <v>0.3724</v>
       </c>
       <c r="J38" t="n">
-        <v>10.74</v>
+        <v>11.172</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1132</v>
+        <v>0.1293</v>
       </c>
       <c r="J39" t="n">
-        <v>3.396</v>
+        <v>3.879</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0978</v>
+        <v>0.1134</v>
       </c>
       <c r="J40" t="n">
-        <v>2.934</v>
+        <v>3.402</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3143</v>
+        <v>-0.3233</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.429</v>
+        <v>-9.699</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8319</v>
+        <v>0.7755</v>
       </c>
       <c r="J42" t="n">
-        <v>23.2932</v>
+        <v>21.714</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6066</v>
+        <v>0.5773</v>
       </c>
       <c r="J43" t="n">
-        <v>16.9848</v>
+        <v>16.1644</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1731</v>
+        <v>-0.1748</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.8468</v>
+        <v>-4.8944</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2997</v>
+        <v>-0.2943</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.3916</v>
+        <v>-8.240399999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6312</v>
+        <v>-0.5945</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.6736</v>
+        <v>-16.646</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8588</v>
+        <v>0.819</v>
       </c>
       <c r="J47" t="n">
-        <v>24.0464</v>
+        <v>22.932</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2127</v>
+        <v>0.2233</v>
       </c>
       <c r="J48" t="n">
-        <v>5.9556</v>
+        <v>6.2524</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0422</v>
+        <v>-0.0475</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.1816</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1303</v>
+        <v>-0.141</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.6484</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1526</v>
+        <v>-0.1639</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.2728</v>
+        <v>-4.5892</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1382</v>
+        <v>1.0964</v>
       </c>
       <c r="J52" t="n">
-        <v>31.8696</v>
+        <v>30.6992</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681</v>
+        <v>0.8132</v>
       </c>
       <c r="J53" t="n">
-        <v>24.3068</v>
+        <v>22.7696</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5533</v>
+        <v>0.5352</v>
       </c>
       <c r="J54" t="n">
-        <v>15.4924</v>
+        <v>14.9856</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3225</v>
+        <v>-0.3102</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.685600000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9777</v>
+        <v>-0.8942</v>
       </c>
       <c r="J56" t="n">
-        <v>-27.3756</v>
+        <v>-25.0376</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2192</v>
+        <v>0.2228</v>
       </c>
       <c r="J57" t="n">
-        <v>6.1376</v>
+        <v>6.2384</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1521</v>
+        <v>0.1571</v>
       </c>
       <c r="J58" t="n">
-        <v>4.2588</v>
+        <v>4.3988</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0591</v>
+        <v>-0.0694</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.6548</v>
+        <v>-1.9432</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.3296</v>
+        <v>-2.6684</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3299</v>
+        <v>-0.3427</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.2372</v>
+        <v>-9.595599999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1832</v>
+        <v>-0.2071</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.8472</v>
+        <v>-4.3491</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.194</v>
+        <v>-0.2176</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.074</v>
+        <v>-4.5696</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.62</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3664</v>
+        <v>-0.3848</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.6944</v>
+        <v>-8.0808</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.58</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4035</v>
+        <v>-0.4201</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.4735</v>
+        <v>-8.822100000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4222</v>
+        <v>-0.4378</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.866199999999999</v>
+        <v>-9.1938</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.89</v>
       </c>
       <c r="I67" t="n">
-        <v>1.555</v>
+        <v>1.5526</v>
       </c>
       <c r="J67" t="n">
-        <v>32.655</v>
+        <v>32.6046</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.6</v>
       </c>
       <c r="I68" t="n">
-        <v>1.219</v>
+        <v>1.1963</v>
       </c>
       <c r="J68" t="n">
-        <v>25.599</v>
+        <v>25.1223</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.46</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0519</v>
+        <v>1.0116</v>
       </c>
       <c r="J69" t="n">
-        <v>22.0899</v>
+        <v>21.2436</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7497</v>
+        <v>0.7229</v>
       </c>
       <c r="J70" t="n">
-        <v>15.7437</v>
+        <v>15.1809</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4256</v>
+        <v>-0.3893</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.9376</v>
+        <v>-8.1753</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4172</v>
+        <v>0.4268</v>
       </c>
       <c r="J72" t="n">
-        <v>11.6816</v>
+        <v>11.9504</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3809</v>
+        <v>0.3922</v>
       </c>
       <c r="J73" t="n">
-        <v>10.6652</v>
+        <v>10.9816</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3068</v>
+        <v>0.3207</v>
       </c>
       <c r="J74" t="n">
-        <v>8.590400000000001</v>
+        <v>8.9796</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0063</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.2296</v>
+        <v>-0.1764</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3555</v>
+        <v>-0.3646</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.954000000000001</v>
+        <v>-10.2088</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3749</v>
+        <v>0.3773</v>
       </c>
       <c r="J77" t="n">
-        <v>10.4972</v>
+        <v>10.5644</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3472</v>
+        <v>0.3512</v>
       </c>
       <c r="J78" t="n">
-        <v>9.7216</v>
+        <v>9.833600000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0494</v>
+        <v>0.0567</v>
       </c>
       <c r="J79" t="n">
-        <v>1.3832</v>
+        <v>1.5876</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0769</v>
+        <v>-0.0868</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.1532</v>
+        <v>-2.4304</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.64</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3935</v>
+        <v>-0.4028</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.018</v>
+        <v>-11.2784</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5515</v>
+        <v>0.5431</v>
       </c>
       <c r="J82" t="n">
-        <v>19.854</v>
+        <v>19.5516</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5344</v>
+        <v>0.5274</v>
       </c>
       <c r="J83" t="n">
-        <v>19.2384</v>
+        <v>18.9864</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3407</v>
+        <v>0.3472</v>
       </c>
       <c r="J84" t="n">
-        <v>12.2652</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.078</v>
+        <v>0.0902</v>
       </c>
       <c r="J85" t="n">
-        <v>2.808</v>
+        <v>3.2472</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3083</v>
+        <v>-0.3185</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.0988</v>
+        <v>-11.466</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6107</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>21.9852</v>
+        <v>20.8836</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2224</v>
+        <v>0.2259</v>
       </c>
       <c r="J88" t="n">
-        <v>8.006399999999999</v>
+        <v>8.132400000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.191</v>
+        <v>0.196</v>
       </c>
       <c r="J89" t="n">
-        <v>6.876</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2969</v>
+        <v>-0.2924</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.6884</v>
+        <v>-10.5264</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3845</v>
+        <v>-0.3731</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.842</v>
+        <v>-13.4316</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.77</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.2135</v>
+        <v>-0.239</v>
       </c>
       <c r="J92" t="n">
-        <v>-4.4835</v>
+        <v>-5.019</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2555</v>
+        <v>-0.2794</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.3655</v>
+        <v>-5.8674</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3512</v>
+        <v>-0.3715</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.3752</v>
+        <v>-7.8015</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.58</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3956</v>
+        <v>-0.414</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.307600000000001</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.43</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5364</v>
+        <v>-0.5458</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.2644</v>
+        <v>-11.4618</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5064</v>
+        <v>1.5019</v>
       </c>
       <c r="J97" t="n">
-        <v>31.6344</v>
+        <v>31.5399</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2522</v>
+        <v>1.2322</v>
       </c>
       <c r="J98" t="n">
-        <v>26.2962</v>
+        <v>25.8762</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0507</v>
+        <v>1.0105</v>
       </c>
       <c r="J99" t="n">
-        <v>22.0647</v>
+        <v>21.2205</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5593</v>
+        <v>0.5547</v>
       </c>
       <c r="J100" t="n">
-        <v>11.7453</v>
+        <v>11.6487</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>0.159</v>
+        <v>0.1895</v>
       </c>
       <c r="J101" t="n">
-        <v>3.339</v>
+        <v>3.9795</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3289</v>
+        <v>0.3261</v>
       </c>
       <c r="J102" t="n">
-        <v>8.8803</v>
+        <v>8.8047</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.014</v>
+        <v>-0.0202</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.378</v>
+        <v>-0.5454</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1212</v>
+        <v>-3.5019</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1266</v>
+        <v>-0.141</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.4182</v>
+        <v>-3.807</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.5914</v>
+        <v>-8.9559</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5158</v>
+        <v>1.4988</v>
       </c>
       <c r="J107" t="n">
-        <v>40.9266</v>
+        <v>40.4676</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8275</v>
+        <v>0.7808</v>
       </c>
       <c r="J108" t="n">
-        <v>22.3425</v>
+        <v>21.0816</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1929</v>
+        <v>0.2058</v>
       </c>
       <c r="J109" t="n">
-        <v>5.2083</v>
+        <v>5.5566</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0395</v>
+        <v>-0.0272</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.0665</v>
+        <v>-0.7344000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.0127</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-27.3429</v>
+        <v>-24.9183</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4308</v>
+        <v>0.4207</v>
       </c>
       <c r="J112" t="n">
-        <v>15.078</v>
+        <v>14.7245</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3921</v>
+        <v>0.3846</v>
       </c>
       <c r="J113" t="n">
-        <v>13.7235</v>
+        <v>13.461</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.96</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0563</v>
+        <v>-0.0673</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.9705</v>
+        <v>-2.3555</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3169</v>
+        <v>-0.3307</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.0915</v>
+        <v>-11.5745</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4386</v>
+        <v>-0.4476</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.351</v>
+        <v>-15.666</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3089</v>
+        <v>1.2757</v>
       </c>
       <c r="J117" t="n">
-        <v>45.8115</v>
+        <v>44.6495</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3546</v>
+        <v>0.3525</v>
       </c>
       <c r="J118" t="n">
-        <v>12.411</v>
+        <v>12.3375</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0785</v>
+        <v>0.0893</v>
       </c>
       <c r="J119" t="n">
-        <v>2.7475</v>
+        <v>3.1255</v>
       </c>
     </row>
     <row r="120">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9678</v>
+        <v>-0.8872</v>
       </c>
       <c r="J121" t="n">
-        <v>-33.873</v>
+        <v>-31.052</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3268</v>
+        <v>0.3289</v>
       </c>
       <c r="J122" t="n">
-        <v>11.438</v>
+        <v>11.5115</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3073</v>
+        <v>0.3104</v>
       </c>
       <c r="J123" t="n">
-        <v>10.7555</v>
+        <v>10.864</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1168</v>
+        <v>0.1251</v>
       </c>
       <c r="J124" t="n">
-        <v>4.088</v>
+        <v>4.3785</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.01</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0383</v>
+        <v>0.0437</v>
       </c>
       <c r="J125" t="n">
-        <v>1.3405</v>
+        <v>1.5295</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3734</v>
+        <v>-0.3837</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.069</v>
+        <v>-13.4295</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0226</v>
+        <v>0.9645</v>
       </c>
       <c r="J127" t="n">
-        <v>35.791</v>
+        <v>33.7575</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.67</v>
+        <v>0.6405</v>
       </c>
       <c r="J128" t="n">
-        <v>23.45</v>
+        <v>22.4175</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4222</v>
+        <v>0.4174</v>
       </c>
       <c r="J129" t="n">
-        <v>14.777</v>
+        <v>14.609</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2594</v>
+        <v>0.2668</v>
       </c>
       <c r="J130" t="n">
-        <v>9.079000000000001</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5444</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.3385</v>
+        <v>-19.054</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.73</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8393</v>
+        <v>0.8288</v>
       </c>
       <c r="J132" t="n">
-        <v>20.1432</v>
+        <v>19.8912</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6119</v>
+        <v>0.618</v>
       </c>
       <c r="J133" t="n">
-        <v>14.6856</v>
+        <v>14.832</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.32</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4089</v>
+        <v>0.4253</v>
       </c>
       <c r="J134" t="n">
-        <v>9.813599999999999</v>
+        <v>10.2072</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1373</v>
+        <v>0.159</v>
       </c>
       <c r="J135" t="n">
-        <v>3.2952</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0828</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.9584</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.21</v>
+        <v>0.1981</v>
       </c>
       <c r="J137" t="n">
-        <v>5.04</v>
+        <v>4.7544</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1735</v>
+        <v>-0.1952</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.164</v>
+        <v>-4.6848</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2352</v>
+        <v>-0.2559</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.6448</v>
+        <v>-6.1416</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4959</v>
+        <v>-0.5057</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.9016</v>
+        <v>-12.1368</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.47</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5145</v>
+        <v>-0.5232</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.348</v>
+        <v>-12.5568</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.681</v>
+        <v>0.6475</v>
       </c>
       <c r="J142" t="n">
-        <v>16.344</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0606</v>
+        <v>0.0598</v>
       </c>
       <c r="J143" t="n">
-        <v>1.4544</v>
+        <v>1.4352</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1346</v>
+        <v>-0.15</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.2304</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1761</v>
+        <v>-0.1923</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.2264</v>
+        <v>-4.6152</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5722</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.7328</v>
+        <v>-13.7784</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.87</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5689</v>
+        <v>1.5612</v>
       </c>
       <c r="J147" t="n">
-        <v>37.6536</v>
+        <v>37.4688</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.946</v>
+        <v>0.893</v>
       </c>
       <c r="J148" t="n">
-        <v>22.704</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9257</v>
+        <v>0.8741</v>
       </c>
       <c r="J149" t="n">
-        <v>22.2168</v>
+        <v>20.9784</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1259</v>
+        <v>-0.109</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.0216</v>
+        <v>-2.616</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5645</v>
+        <v>-0.5223</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.548</v>
+        <v>-12.5352</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0906</v>
+        <v>-0.1132</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.9932</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1144</v>
+        <v>-0.137</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.5168</v>
+        <v>-3.014</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3535</v>
+        <v>-0.3715</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.777</v>
+        <v>-8.173</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.59</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4002</v>
+        <v>-0.416</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.804399999999999</v>
+        <v>-9.151999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.447</v>
+        <v>-0.4602</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.834</v>
+        <v>-10.1244</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.8</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4542</v>
+        <v>1.4461</v>
       </c>
       <c r="J157" t="n">
-        <v>31.9924</v>
+        <v>31.8142</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.77</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="J158" t="n">
-        <v>31.2312</v>
+        <v>31.009</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.58</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1968</v>
+        <v>1.1722</v>
       </c>
       <c r="J159" t="n">
-        <v>26.3296</v>
+        <v>25.7884</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4142</v>
+        <v>0.4232</v>
       </c>
       <c r="J160" t="n">
-        <v>9.112399999999999</v>
+        <v>9.3104</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7212</v>
+        <v>-0.6579</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.8664</v>
+        <v>-14.4738</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2503</v>
+        <v>1.2079</v>
       </c>
       <c r="J162" t="n">
-        <v>36.2587</v>
+        <v>35.0291</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2928</v>
+        <v>0.2895</v>
       </c>
       <c r="J163" t="n">
-        <v>8.491199999999999</v>
+        <v>8.3955</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4312</v>
+        <v>-0.4177</v>
       </c>
       <c r="J164" t="n">
-        <v>-12.5048</v>
+        <v>-12.1133</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.83</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5154</v>
       </c>
       <c r="J165" t="n">
-        <v>-15.6542</v>
+        <v>-14.9466</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.65</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.913</v>
       </c>
       <c r="J166" t="n">
-        <v>-28.8086</v>
+        <v>-26.477</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.22</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4539</v>
+        <v>0.4519</v>
       </c>
       <c r="J167" t="n">
-        <v>13.1631</v>
+        <v>13.1051</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4539</v>
+        <v>0.4519</v>
       </c>
       <c r="J168" t="n">
-        <v>13.1631</v>
+        <v>13.1051</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4362</v>
+        <v>0.4355</v>
       </c>
       <c r="J169" t="n">
-        <v>12.6498</v>
+        <v>12.6295</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0781</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.0445</v>
+        <v>-2.2649</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2962</v>
+        <v>-0.3072</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.5898</v>
+        <v>-8.908799999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1563</v>
+        <v>1.1197</v>
       </c>
       <c r="J172" t="n">
-        <v>33.5327</v>
+        <v>32.4713</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7726</v>
+        <v>0.7342</v>
       </c>
       <c r="J173" t="n">
-        <v>22.4054</v>
+        <v>21.2918</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3864</v>
+        <v>0.387</v>
       </c>
       <c r="J174" t="n">
-        <v>11.2056</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1212</v>
+        <v>0.1392</v>
       </c>
       <c r="J175" t="n">
-        <v>3.5148</v>
+        <v>4.0368</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.99</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1015</v>
+        <v>-0.092</v>
       </c>
       <c r="J176" t="n">
-        <v>-2.9435</v>
+        <v>-2.668</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3137</v>
+        <v>0.315</v>
       </c>
       <c r="J177" t="n">
-        <v>9.097300000000001</v>
+        <v>9.135</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.042</v>
+        <v>0.0464</v>
       </c>
       <c r="J178" t="n">
-        <v>1.218</v>
+        <v>1.3456</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1015</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.1286</v>
+        <v>-2.4418</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2558</v>
+        <v>-0.2697</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.4182</v>
+        <v>-7.8213</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6611</v>
       </c>
       <c r="J182" t="n">
-        <v>28.728</v>
+        <v>27.7662</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.13</v>
       </c>
       <c r="I183" t="n">
-        <v>0.294</v>
+        <v>0.3007</v>
       </c>
       <c r="J183" t="n">
-        <v>12.348</v>
+        <v>12.6294</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0597</v>
+        <v>0.0689</v>
       </c>
       <c r="J184" t="n">
-        <v>2.5074</v>
+        <v>2.8938</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0549</v>
+        <v>-0.0619</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.3058</v>
+        <v>-2.5998</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2646</v>
+        <v>-0.2765</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.1132</v>
+        <v>-11.613</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1619</v>
+        <v>1.115</v>
       </c>
       <c r="J187" t="n">
-        <v>48.7998</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5148</v>
       </c>
       <c r="J188" t="n">
-        <v>22.6296</v>
+        <v>21.6216</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2924</v>
+        <v>-0.2892</v>
       </c>
       <c r="J189" t="n">
-        <v>-12.2808</v>
+        <v>-12.1464</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.82</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5425</v>
       </c>
       <c r="J190" t="n">
-        <v>-23.9862</v>
+        <v>-22.785</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9738</v>
+        <v>-0.8953</v>
       </c>
       <c r="J191" t="n">
-        <v>-40.8996</v>
+        <v>-37.6026</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.66</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7798</v>
       </c>
       <c r="J192" t="n">
-        <v>18.9552</v>
+        <v>18.7152</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.55</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6728</v>
+        <v>0.6717</v>
       </c>
       <c r="J193" t="n">
-        <v>16.1472</v>
+        <v>16.1208</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0736</v>
+        <v>0.0907</v>
       </c>
       <c r="J194" t="n">
-        <v>1.7664</v>
+        <v>2.1768</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1231</v>
+        <v>-0.1295</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.9544</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1231</v>
+        <v>-0.1295</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.9544</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.09</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2344</v>
+        <v>0.2285</v>
       </c>
       <c r="J197" t="n">
-        <v>5.6256</v>
+        <v>5.484</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0785</v>
+        <v>0.0709</v>
       </c>
       <c r="J198" t="n">
-        <v>1.884</v>
+        <v>1.7016</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2614</v>
+        <v>-0.28</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.2736</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.403</v>
+        <v>-0.4166</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.672000000000001</v>
+        <v>-9.9984</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.49</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.505</v>
+        <v>-0.513</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.12</v>
+        <v>-12.312</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.88</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1306</v>
+        <v>-0.1497</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.7426</v>
+        <v>-3.1437</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.84</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1737</v>
+        <v>-0.193</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.6477</v>
+        <v>-4.053</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.214</v>
+        <v>-0.2331</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.494</v>
+        <v>-4.8951</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.73</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2795</v>
+        <v>-0.2979</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.8695</v>
+        <v>-6.2559</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3458</v>
+        <v>-0.362</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.2618</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.76</v>
       </c>
       <c r="I207" t="n">
-        <v>1.443</v>
+        <v>1.4281</v>
       </c>
       <c r="J207" t="n">
-        <v>30.303</v>
+        <v>29.9901</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6652</v>
+        <v>0.6421</v>
       </c>
       <c r="J208" t="n">
-        <v>13.9692</v>
+        <v>13.4841</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.15</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4204</v>
+        <v>0.4221</v>
       </c>
       <c r="J209" t="n">
-        <v>8.8284</v>
+        <v>8.864100000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3674</v>
+        <v>0.3738</v>
       </c>
       <c r="J210" t="n">
-        <v>7.7154</v>
+        <v>7.8498</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.256</v>
+        <v>0.2713</v>
       </c>
       <c r="J211" t="n">
-        <v>5.376</v>
+        <v>5.6973</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.61</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2521</v>
+        <v>1.2276</v>
       </c>
       <c r="J212" t="n">
-        <v>31.3025</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.48</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0923</v>
+        <v>1.0553</v>
       </c>
       <c r="J213" t="n">
-        <v>27.3075</v>
+        <v>26.3825</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6107</v>
+        <v>0.5951</v>
       </c>
       <c r="J214" t="n">
-        <v>15.2675</v>
+        <v>14.8775</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5868</v>
+        <v>0.5737</v>
       </c>
       <c r="J215" t="n">
-        <v>14.67</v>
+        <v>14.3425</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0914</v>
+        <v>0.1184</v>
       </c>
       <c r="J216" t="n">
-        <v>2.285</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0626</v>
+        <v>-0.0794</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.565</v>
+        <v>-1.985</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0992</v>
+        <v>-0.1171</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.48</v>
+        <v>-2.9275</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1109</v>
+        <v>-0.129</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.7725</v>
+        <v>-3.225</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.72</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2912</v>
+        <v>-0.3089</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.28</v>
+        <v>-7.7225</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4787</v>
+        <v>-0.488</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.9675</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7825</v>
+        <v>0.7454</v>
       </c>
       <c r="J222" t="n">
-        <v>20.345</v>
+        <v>19.3804</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7599</v>
+        <v>0.7254</v>
       </c>
       <c r="J223" t="n">
-        <v>19.7574</v>
+        <v>18.8604</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6471</v>
+        <v>0.6249</v>
       </c>
       <c r="J224" t="n">
-        <v>16.8246</v>
+        <v>16.2474</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.21</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5772</v>
+        <v>0.5621</v>
       </c>
       <c r="J225" t="n">
-        <v>15.0072</v>
+        <v>14.6146</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.5039</v>
+        <v>0.4962</v>
       </c>
       <c r="J226" t="n">
-        <v>13.1014</v>
+        <v>12.9012</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.361</v>
+        <v>0.3498</v>
       </c>
       <c r="J227" t="n">
-        <v>9.385999999999999</v>
+        <v>9.094799999999999</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1066</v>
+        <v>0.1028</v>
       </c>
       <c r="J228" t="n">
-        <v>2.7716</v>
+        <v>2.6728</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2403</v>
+        <v>-0.2576</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.2478</v>
+        <v>-6.6976</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2792</v>
+        <v>-0.2957</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2592</v>
+        <v>-7.6882</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.58</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4302</v>
+        <v>-0.441</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.1852</v>
+        <v>-11.466</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.43</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0519</v>
+        <v>1.0023</v>
       </c>
       <c r="J232" t="n">
-        <v>27.3494</v>
+        <v>26.0598</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9091</v>
+        <v>0.8541</v>
       </c>
       <c r="J233" t="n">
-        <v>23.6366</v>
+        <v>22.2066</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8868</v>
+        <v>0.8343</v>
       </c>
       <c r="J234" t="n">
-        <v>23.0568</v>
+        <v>21.6918</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3039</v>
+        <v>0.3112</v>
       </c>
       <c r="J235" t="n">
-        <v>7.9014</v>
+        <v>8.091200000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8004</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="J236" t="n">
-        <v>-20.8104</v>
+        <v>-19.1464</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.21</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4788</v>
+        <v>0.4666</v>
       </c>
       <c r="J237" t="n">
-        <v>12.4488</v>
+        <v>12.1316</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.05</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1537</v>
+        <v>0.1583</v>
       </c>
       <c r="J238" t="n">
-        <v>3.9962</v>
+        <v>4.1158</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0154</v>
+        <v>-0.0214</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.4004</v>
+        <v>-0.5564</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3005</v>
+        <v>-0.3142</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.813</v>
+        <v>-8.1692</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3101</v>
+        <v>-0.3236</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.0626</v>
+        <v>-8.413600000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2281</v>
+        <v>0.2379</v>
       </c>
       <c r="J242" t="n">
-        <v>5.7025</v>
+        <v>5.9475</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.09</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1674</v>
+        <v>0.1783</v>
       </c>
       <c r="J243" t="n">
-        <v>4.185</v>
+        <v>4.4575</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1516</v>
+        <v>0.1626</v>
       </c>
       <c r="J244" t="n">
-        <v>3.79</v>
+        <v>4.065</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0389</v>
+        <v>-0.0449</v>
       </c>
       <c r="J245" t="n">
-        <v>-0.9725</v>
+        <v>-1.1225</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.88</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1597</v>
+        <v>-0.1721</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.9925</v>
+        <v>-4.3025</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6609</v>
+        <v>0.6574</v>
       </c>
       <c r="J247" t="n">
-        <v>16.5225</v>
+        <v>16.435</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2633</v>
+        <v>0.2795</v>
       </c>
       <c r="J248" t="n">
-        <v>6.5825</v>
+        <v>6.9875</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2381</v>
+        <v>0.2546</v>
       </c>
       <c r="J249" t="n">
-        <v>5.9525</v>
+        <v>6.365</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0116</v>
+        <v>0.0208</v>
       </c>
       <c r="J250" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2535</v>
+        <v>-0.2638</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.3375</v>
+        <v>-6.595</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.46</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1307</v>
+        <v>1.0848</v>
       </c>
       <c r="J252" t="n">
-        <v>33.921</v>
+        <v>32.544</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.12</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3872</v>
+        <v>0.3812</v>
       </c>
       <c r="J253" t="n">
-        <v>11.616</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0427</v>
+        <v>0.0515</v>
       </c>
       <c r="J254" t="n">
-        <v>1.281</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2443</v>
+        <v>-0.241</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.329</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7654</v>
+        <v>-0.7117</v>
       </c>
       <c r="J256" t="n">
-        <v>-22.962</v>
+        <v>-21.351</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.6</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0357</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="J257" t="n">
-        <v>31.071</v>
+        <v>29.895</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1674</v>
+        <v>0.1801</v>
       </c>
       <c r="J258" t="n">
-        <v>5.022</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1674</v>
+        <v>0.1801</v>
       </c>
       <c r="J259" t="n">
-        <v>5.022</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0946</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.607</v>
+        <v>-2.838</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2101</v>
+        <v>-0.2211</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.303</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.86</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1443</v>
+        <v>-0.1654</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.6075</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.82</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1873</v>
+        <v>-0.2081</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.6825</v>
+        <v>-5.2025</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2376</v>
+        <v>-0.2577</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.94</v>
+        <v>-6.4425</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.63</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3676</v>
+        <v>-0.3841</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.19</v>
+        <v>-9.602499999999999</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.62</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3769</v>
+        <v>-0.393</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.422499999999999</v>
+        <v>-9.824999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.88</v>
       </c>
       <c r="I267" t="n">
-        <v>1.5667</v>
+        <v>1.5611</v>
       </c>
       <c r="J267" t="n">
-        <v>39.1675</v>
+        <v>39.0275</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0635</v>
+        <v>1.0226</v>
       </c>
       <c r="J268" t="n">
-        <v>26.5875</v>
+        <v>25.565</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.34</v>
       </c>
       <c r="I269" t="n">
-        <v>0.8537</v>
+        <v>0.8116</v>
       </c>
       <c r="J269" t="n">
-        <v>21.3425</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.04</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0859</v>
+        <v>0.1146</v>
       </c>
       <c r="J270" t="n">
-        <v>2.1475</v>
+        <v>2.865</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.98</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1779</v>
+        <v>-0.1582</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.4475</v>
+        <v>-3.955</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.49</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0709</v>
+        <v>1.012</v>
       </c>
       <c r="J272" t="n">
-        <v>21.418</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.63</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.3688</v>
+        <v>-0.385</v>
       </c>
       <c r="J273" t="n">
-        <v>-7.376</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.58</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4156</v>
+        <v>-0.4296</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.311999999999999</v>
+        <v>-8.592000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.58</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4156</v>
+        <v>-0.4296</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.311999999999999</v>
+        <v>-8.592000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5272</v>
+        <v>-0.5346</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.544</v>
+        <v>-10.692</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.58</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2132</v>
+        <v>1.1865</v>
       </c>
       <c r="J277" t="n">
-        <v>24.264</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.49</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1027</v>
+        <v>1.0674</v>
       </c>
       <c r="J278" t="n">
-        <v>22.054</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.37</v>
       </c>
       <c r="I279" t="n">
-        <v>0.9185</v>
+        <v>0.8689</v>
       </c>
       <c r="J279" t="n">
-        <v>18.37</v>
+        <v>17.378</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.31</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7912</v>
+        <v>0.7559</v>
       </c>
       <c r="J280" t="n">
-        <v>15.824</v>
+        <v>15.118</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.89</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4619</v>
+        <v>-0.4274</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.238</v>
+        <v>-8.548</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0508</v>
+        <v>0.0368</v>
       </c>
       <c r="J282" t="n">
-        <v>1.1176</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="J283" t="n">
-        <v>0.2376</v>
+        <v>-0.1056</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0529</v>
+        <v>-0.0684</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.1638</v>
+        <v>-1.5048</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4346</v>
+        <v>-0.446</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.561199999999999</v>
+        <v>-9.811999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4439</v>
+        <v>-0.4548</v>
       </c>
       <c r="J286" t="n">
-        <v>-9.7658</v>
+        <v>-10.0056</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.77</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4242</v>
+        <v>1.4135</v>
       </c>
       <c r="J287" t="n">
-        <v>31.3324</v>
+        <v>31.097</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1041</v>
+        <v>1.0713</v>
       </c>
       <c r="J288" t="n">
-        <v>24.2902</v>
+        <v>23.5686</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.44</v>
       </c>
       <c r="I289" t="n">
-        <v>1.0289</v>
+        <v>0.9838</v>
       </c>
       <c r="J289" t="n">
-        <v>22.6358</v>
+        <v>21.6436</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.929</v>
+        <v>0.8806</v>
       </c>
       <c r="J290" t="n">
-        <v>20.438</v>
+        <v>19.3732</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4192</v>
+        <v>-0.3848</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.2224</v>
+        <v>-8.4656</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.37</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4844</v>
+        <v>0.4934</v>
       </c>
       <c r="J292" t="n">
-        <v>12.5944</v>
+        <v>12.8284</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.21</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2963</v>
+        <v>0.3128</v>
       </c>
       <c r="J293" t="n">
-        <v>7.7038</v>
+        <v>8.1328</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2597</v>
+        <v>0.2769</v>
       </c>
       <c r="J294" t="n">
-        <v>6.7522</v>
+        <v>7.1994</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2227</v>
+        <v>0.24</v>
       </c>
       <c r="J295" t="n">
-        <v>5.7902</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1058</v>
+        <v>-0.1128</v>
       </c>
       <c r="J296" t="n">
-        <v>-2.7508</v>
+        <v>-2.9328</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1531</v>
+        <v>0.1551</v>
       </c>
       <c r="J297" t="n">
-        <v>3.9806</v>
+        <v>4.0326</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0892</v>
       </c>
       <c r="J298" t="n">
-        <v>-1.9578</v>
+        <v>-2.3192</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1106</v>
+        <v>-0.1259</v>
       </c>
       <c r="J299" t="n">
-        <v>-2.8756</v>
+        <v>-3.2734</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1217</v>
+        <v>-0.1374</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.1642</v>
+        <v>-3.5724</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.54</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4696</v>
+        <v>-0.4779</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.2096</v>
+        <v>-12.4254</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.28</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6227</v>
+        <v>0.5954</v>
       </c>
       <c r="J302" t="n">
-        <v>14.9448</v>
+        <v>14.2896</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.98</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0269</v>
+        <v>-0.0358</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.6456</v>
+        <v>-0.8592</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1974</v>
+        <v>-0.2135</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.7376</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1974</v>
+        <v>-0.2135</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.7376</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.61</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4095</v>
+        <v>-0.4201</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.827999999999999</v>
+        <v>-10.0824</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.46</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1003</v>
+        <v>1.0573</v>
       </c>
       <c r="J307" t="n">
-        <v>26.4072</v>
+        <v>25.3752</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5675</v>
+        <v>0.5502</v>
       </c>
       <c r="J308" t="n">
-        <v>13.62</v>
+        <v>13.2048</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.17</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4939</v>
+        <v>0.4837</v>
       </c>
       <c r="J309" t="n">
-        <v>11.8536</v>
+        <v>11.6088</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1627</v>
+        <v>0.1767</v>
       </c>
       <c r="J310" t="n">
-        <v>3.9048</v>
+        <v>4.2408</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.91</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3635</v>
+        <v>-0.3456</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.724</v>
+        <v>-8.2944</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.54</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1614</v>
+        <v>1.1315</v>
       </c>
       <c r="J312" t="n">
-        <v>24.3894</v>
+        <v>23.7615</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.47</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0754</v>
+        <v>1.0368</v>
       </c>
       <c r="J313" t="n">
-        <v>22.5834</v>
+        <v>21.7728</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.35</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8741</v>
+        <v>0.8298</v>
       </c>
       <c r="J314" t="n">
-        <v>18.3561</v>
+        <v>17.4258</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.23</v>
       </c>
       <c r="I315" t="n">
-        <v>0.6049</v>
+        <v>0.5911</v>
       </c>
       <c r="J315" t="n">
-        <v>12.7029</v>
+        <v>12.4131</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.13</v>
       </c>
       <c r="I316" t="n">
-        <v>0.352</v>
+        <v>0.3631</v>
       </c>
       <c r="J316" t="n">
-        <v>7.392</v>
+        <v>7.6251</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3746</v>
+        <v>0.3556</v>
       </c>
       <c r="J317" t="n">
-        <v>7.8666</v>
+        <v>7.4676</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0238</v>
+        <v>0.0013</v>
       </c>
       <c r="J318" t="n">
-        <v>0.4998</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0596</v>
+        <v>-0.077</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.2516</v>
+        <v>-1.617</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.44</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5505</v>
+        <v>-0.5556</v>
       </c>
       <c r="J320" t="n">
-        <v>-11.5605</v>
+        <v>-11.6676</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.43</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5596</v>
+        <v>-0.5641</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.7516</v>
+        <v>-11.8461</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.54</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2028</v>
+        <v>1.168</v>
       </c>
       <c r="J322" t="n">
-        <v>31.2728</v>
+        <v>30.368</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.45</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0861</v>
+        <v>1.0414</v>
       </c>
       <c r="J323" t="n">
-        <v>28.2386</v>
+        <v>27.0764</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.04</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1287</v>
+        <v>0.1444</v>
       </c>
       <c r="J324" t="n">
-        <v>3.3462</v>
+        <v>3.7544</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.0389</v>
+        <v>-0.0268</v>
       </c>
       <c r="J325" t="n">
-        <v>-1.0114</v>
+        <v>-0.6968</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6644</v>
       </c>
       <c r="J326" t="n">
-        <v>-18.6472</v>
+        <v>-17.2744</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1584</v>
+        <v>0.1617</v>
       </c>
       <c r="J327" t="n">
-        <v>4.1184</v>
+        <v>4.2042</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1064</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.4258</v>
+        <v>-2.7664</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.91</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.9978</v>
+        <v>-3.367</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1582</v>
+        <v>-0.1735</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.1132</v>
+        <v>-4.511</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.86</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1687</v>
+        <v>-0.1841</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.3862</v>
+        <v>-4.7866</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.3</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6509</v>
+        <v>0.6223</v>
       </c>
       <c r="J332" t="n">
-        <v>17.5743</v>
+        <v>16.8021</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3108</v>
+        <v>0.3086</v>
       </c>
       <c r="J333" t="n">
-        <v>8.3916</v>
+        <v>8.3322</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2047</v>
+        <v>0.2069</v>
       </c>
       <c r="J334" t="n">
-        <v>5.5269</v>
+        <v>5.5863</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.346</v>
+        <v>-0.3588</v>
       </c>
       <c r="J335" t="n">
-        <v>-9.342000000000001</v>
+        <v>-9.6876</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5656</v>
+        <v>-0.5675</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.2712</v>
+        <v>-15.3225</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.82</v>
       </c>
       <c r="I337" t="n">
-        <v>1.5671</v>
+        <v>1.5502</v>
       </c>
       <c r="J337" t="n">
-        <v>42.3117</v>
+        <v>41.8554</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.12</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3724</v>
+        <v>0.3711</v>
       </c>
       <c r="J338" t="n">
-        <v>10.0548</v>
+        <v>10.0197</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2905</v>
+        <v>0.2952</v>
       </c>
       <c r="J339" t="n">
-        <v>7.8435</v>
+        <v>7.9704</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.86</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4975</v>
+        <v>-0.4697</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.4325</v>
+        <v>-12.6819</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.75</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7845</v>
+        <v>-0.7252</v>
       </c>
       <c r="J341" t="n">
-        <v>-21.1815</v>
+        <v>-19.5804</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5502</v>
+        <v>0.539</v>
       </c>
       <c r="J342" t="n">
-        <v>26.4096</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.21</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4442</v>
+        <v>0.4413</v>
       </c>
       <c r="J343" t="n">
-        <v>21.3216</v>
+        <v>21.1824</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0325</v>
+        <v>0.0397</v>
       </c>
       <c r="J344" t="n">
-        <v>1.56</v>
+        <v>1.9056</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1277</v>
+        <v>-0.139</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.1296</v>
+        <v>-6.672</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2338</v>
+        <v>-0.2462</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.2224</v>
+        <v>-11.8176</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7637</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J347" t="n">
-        <v>36.6576</v>
+        <v>34.5264</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7393</v>
+        <v>0.6979</v>
       </c>
       <c r="J348" t="n">
-        <v>35.4864</v>
+        <v>33.4992</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.22</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6405</v>
+        <v>0.6106</v>
       </c>
       <c r="J349" t="n">
-        <v>30.744</v>
+        <v>29.3088</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5111</v>
+        <v>-0.4847</v>
       </c>
       <c r="J350" t="n">
-        <v>-24.5328</v>
+        <v>-23.2656</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6696</v>
+        <v>-0.6262</v>
       </c>
       <c r="J351" t="n">
-        <v>-32.1408</v>
+        <v>-30.0576</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5454/event_5454_evp_summary.xlsx
+++ b/database/event/5454/event_5454_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.4851</v>
+        <v>3.3574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5674</v>
+        <v>0.5466</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9623</v>
+        <v>0.9237</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4851</v>
+        <v>3.3574</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4851</v>
+        <v>3.3574</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9029</v>
+        <v>4.7441</v>
       </c>
       <c r="I2" t="n">
-        <v>6.0096</v>
+        <v>5.8584</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0096</v>
+        <v>5.8584</v>
       </c>
       <c r="N2" t="n">
         <v>298</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2514</v>
+        <v>3.1379</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5293</v>
+        <v>0.5109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8559</v>
+        <v>0.8237</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2514</v>
+        <v>3.1379</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2514</v>
+        <v>3.1379</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3913</v>
+        <v>4.241</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8095</v>
+        <v>5.6683</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8095</v>
+        <v>5.6683</v>
       </c>
       <c r="N3" t="n">
         <v>394</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2065</v>
+        <v>3.0993</v>
       </c>
       <c r="C4" t="n">
-        <v>0.522</v>
+        <v>0.5046</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8355</v>
+        <v>0.8061</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2065</v>
+        <v>3.0993</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2065</v>
+        <v>3.0993</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.293</v>
+        <v>4.1524</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2621</v>
+        <v>5.1277</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2621</v>
+        <v>5.1277</v>
       </c>
       <c r="N4" t="n">
         <v>298</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1145</v>
+        <v>2.963</v>
       </c>
       <c r="C5" t="n">
-        <v>0.507</v>
+        <v>0.4824</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7936</v>
+        <v>0.744</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1145</v>
+        <v>2.963</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1145</v>
+        <v>2.963</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0918</v>
+        <v>3.8401</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6469</v>
+        <v>4.3813</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6469</v>
+        <v>4.3813</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0991</v>
+        <v>2.9617</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4822</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7866</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0991</v>
+        <v>2.9617</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0991</v>
+        <v>2.9617</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.058</v>
+        <v>3.8372</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3799</v>
+        <v>4.1531</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3799</v>
+        <v>4.1531</v>
       </c>
       <c r="N6" t="n">
         <v>198</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.029</v>
+        <v>2.898</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4931</v>
+        <v>0.4718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7547</v>
+        <v>0.7144</v>
       </c>
       <c r="E7" t="n">
-        <v>3.029</v>
+        <v>2.898</v>
       </c>
       <c r="F7" t="n">
-        <v>3.029</v>
+        <v>2.898</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9046</v>
+        <v>3.6913</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1656</v>
+        <v>4.9336</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.1656</v>
+        <v>4.9336</v>
       </c>
       <c r="N7" t="n">
         <v>394</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9183</v>
+        <v>2.8391</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4751</v>
+        <v>0.4622</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7043</v>
+        <v>0.6876</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9183</v>
+        <v>2.8391</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9183</v>
+        <v>2.8391</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6623</v>
+        <v>3.5562</v>
       </c>
       <c r="I8" t="n">
-        <v>4.489</v>
+        <v>4.3914</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.489</v>
+        <v>4.3914</v>
       </c>
       <c r="N8" t="n">
         <v>298</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6174</v>
+        <v>2.568</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4261</v>
+        <v>0.4181</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5673</v>
+        <v>0.5641</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6174</v>
+        <v>2.568</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6174</v>
+        <v>2.568</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0038</v>
+        <v>2.935</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2421</v>
+        <v>3.1767</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2421</v>
+        <v>3.1767</v>
       </c>
       <c r="N9" t="n">
         <v>166</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5112</v>
+        <v>2.433</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4088</v>
+        <v>0.3961</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5189</v>
+        <v>0.5026</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5112</v>
+        <v>2.433</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5112</v>
+        <v>2.433</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7712</v>
+        <v>2.6255</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6662</v>
+        <v>3.5091</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6662</v>
+        <v>3.5091</v>
       </c>
       <c r="N10" t="n">
         <v>394</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3909</v>
+        <v>2.406</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3892</v>
+        <v>0.3917</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4642</v>
+        <v>0.4903</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3909</v>
+        <v>2.406</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3909</v>
+        <v>2.406</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5079</v>
+        <v>2.5637</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7766</v>
+        <v>2.8489</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7766</v>
+        <v>2.8489</v>
       </c>
       <c r="N11" t="n">
         <v>252</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3342</v>
+        <v>2.2669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.38</v>
+        <v>0.3691</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4384</v>
+        <v>0.4269</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3342</v>
+        <v>2.2669</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3342</v>
+        <v>2.2669</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3838</v>
+        <v>2.2669</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6392</v>
+        <v>2.5191</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6392</v>
+        <v>2.5191</v>
       </c>
       <c r="N12" t="n">
         <v>252</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2569</v>
+        <v>2.2038</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3674</v>
+        <v>0.3588</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4032</v>
+        <v>0.3981</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2569</v>
+        <v>2.2038</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2569</v>
+        <v>2.2038</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2569</v>
+        <v>2.2038</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5631</v>
+        <v>2.5144</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5631</v>
+        <v>2.5144</v>
       </c>
       <c r="N13" t="n">
         <v>297</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0198</v>
+        <v>1.9004</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3288</v>
+        <v>0.3094</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2953</v>
+        <v>0.2599</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0198</v>
+        <v>1.9004</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0198</v>
+        <v>1.9004</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0198</v>
+        <v>1.9004</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4757</v>
+        <v>2.3467</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4757</v>
+        <v>2.3467</v>
       </c>
       <c r="N14" t="n">
         <v>298</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9021</v>
+        <v>1.6768</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3097</v>
+        <v>0.273</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2417</v>
+        <v>0.1581</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9021</v>
+        <v>1.6768</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9021</v>
+        <v>1.6768</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9021</v>
+        <v>1.6768</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9511</v>
+        <v>1.7216</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9511</v>
+        <v>1.7216</v>
       </c>
       <c r="N15" t="n">
         <v>162</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8125</v>
+        <v>1.6592</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2951</v>
+        <v>0.2701</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2009</v>
+        <v>0.1501</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8125</v>
+        <v>1.6592</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8125</v>
+        <v>1.6592</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8125</v>
+        <v>1.6592</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0584</v>
+        <v>1.8931</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0584</v>
+        <v>1.8931</v>
       </c>
       <c r="N16" t="n">
         <v>297</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5816</v>
+        <v>1.5532</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2575</v>
+        <v>0.2529</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0958</v>
+        <v>0.1018</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5816</v>
+        <v>1.5532</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5816</v>
+        <v>1.5532</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5816</v>
+        <v>1.5532</v>
       </c>
       <c r="I17" t="n">
-        <v>1.707</v>
+        <v>1.681</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.707</v>
+        <v>1.681</v>
       </c>
       <c r="N17" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5811</v>
+        <v>1.4827</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2574</v>
+        <v>0.2414</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0955</v>
+        <v>0.0697</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5811</v>
+        <v>1.4827</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5811</v>
+        <v>1.4827</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5811</v>
+        <v>1.4827</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7065</v>
+        <v>1.6048</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7065</v>
+        <v>1.6048</v>
       </c>
       <c r="N18" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2611</v>
+        <v>1.2186</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2053</v>
+        <v>0.1984</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0501</v>
+        <v>-0.0507</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2611</v>
+        <v>1.2186</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2611</v>
+        <v>1.2186</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2611</v>
+        <v>1.2186</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6684</v>
+        <v>1.2186</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>394</v>
+        <v>103</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6684</v>
+        <v>1.2186</v>
       </c>
       <c r="N19" t="n">
-        <v>394</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2583</v>
+        <v>1.1573</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2049</v>
+        <v>0.1884</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0514</v>
+        <v>-0.0786</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2583</v>
+        <v>1.1573</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2583</v>
+        <v>1.1573</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2583</v>
+        <v>1.1573</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2583</v>
+        <v>1.5468</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2583</v>
+        <v>1.5468</v>
       </c>
       <c r="N20" t="n">
-        <v>103</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.132</v>
+        <v>1.0738</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1843</v>
+        <v>0.1748</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1089</v>
+        <v>-0.1166</v>
       </c>
       <c r="E21" t="n">
-        <v>1.132</v>
+        <v>1.0738</v>
       </c>
       <c r="F21" t="n">
-        <v>1.132</v>
+        <v>1.0738</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.132</v>
+        <v>1.0738</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2218</v>
+        <v>1.1622</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2218</v>
+        <v>1.1622</v>
       </c>
       <c r="N21" t="n">
         <v>166</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0156</v>
+        <v>0.921</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1653</v>
+        <v>0.1499</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1619</v>
+        <v>-0.1862</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0156</v>
+        <v>0.921</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0156</v>
+        <v>0.921</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0156</v>
+        <v>0.921</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0961</v>
+        <v>0.9968</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0961</v>
+        <v>0.9968</v>
       </c>
       <c r="N22" t="n">
         <v>198</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9325</v>
+        <v>0.7801</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1518</v>
+        <v>0.127</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1997</v>
+        <v>-0.2504</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9325</v>
+        <v>0.7801</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9325</v>
+        <v>0.7801</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9325</v>
+        <v>0.7801</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0065</v>
+        <v>0.8444</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0065</v>
+        <v>0.8444</v>
       </c>
       <c r="N23" t="n">
         <v>198</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7352</v>
+        <v>0.6055</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1197</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2895</v>
+        <v>-0.33</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7352</v>
+        <v>0.6055</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7352</v>
+        <v>0.6055</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7352</v>
+        <v>0.6055</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7541</v>
+        <v>0.6217</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7541</v>
+        <v>0.6217</v>
       </c>
       <c r="N24" t="n">
         <v>162</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>HEAP</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5592</v>
+        <v>0.4537</v>
       </c>
       <c r="C25" t="n">
-        <v>0.091</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3696</v>
+        <v>-0.3991</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5592</v>
+        <v>0.4537</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5592</v>
+        <v>0.4537</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5592</v>
+        <v>0.4537</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5736</v>
+        <v>0.4911</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5736</v>
+        <v>0.4911</v>
       </c>
       <c r="N25" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEAP</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4621</v>
+        <v>0.4216</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0752</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4138</v>
+        <v>-0.4137</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4621</v>
+        <v>0.4216</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4621</v>
+        <v>0.4216</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4621</v>
+        <v>0.4216</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4988</v>
+        <v>0.4329</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4988</v>
+        <v>0.4329</v>
       </c>
       <c r="N26" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0653</v>
+        <v>0.141</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0106</v>
+        <v>0.023</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5945</v>
+        <v>-0.5416</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0653</v>
+        <v>0.141</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0653</v>
+        <v>0.141</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0653</v>
+        <v>0.141</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0801</v>
+        <v>0.1741</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0801</v>
+        <v>0.1741</v>
       </c>
       <c r="N27" t="n">
         <v>298</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0046</v>
+        <v>0.1023</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0007</v>
+        <v>0.0167</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6263</v>
+        <v>-0.5592</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0046</v>
+        <v>0.1023</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0046</v>
+        <v>0.1023</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0046</v>
+        <v>0.1023</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0051</v>
+        <v>0.1137</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0051</v>
+        <v>0.1137</v>
       </c>
       <c r="N28" t="n">
         <v>252</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1462</v>
+        <v>-0.1754</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0238</v>
+        <v>-0.0286</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6908</v>
+        <v>-0.6857</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1462</v>
+        <v>-0.1754</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1462</v>
+        <v>-0.1754</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1462</v>
+        <v>-0.1754</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1934</v>
+        <v>-0.1898</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1934</v>
+        <v>-0.1898</v>
       </c>
       <c r="N29" t="n">
-        <v>394</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.218</v>
+        <v>-0.2636</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0355</v>
+        <v>-0.0429</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7234</v>
+        <v>-0.7259</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.218</v>
+        <v>-0.2636</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.218</v>
+        <v>-0.2636</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.218</v>
+        <v>-0.2636</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2353</v>
+        <v>-0.3523</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2353</v>
+        <v>-0.3523</v>
       </c>
       <c r="N30" t="n">
-        <v>198</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0583</v>
+        <v>-0.0604</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7872</v>
+        <v>-0.7749</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3581</v>
+        <v>-0.3712</v>
       </c>
       <c r="N31" t="n">
         <v>103</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4246</v>
+        <v>-0.3773</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0614</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8175</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4246</v>
+        <v>-0.3773</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4246</v>
+        <v>-0.3773</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4246</v>
+        <v>-0.3773</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4246</v>
+        <v>-0.4193</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4246</v>
+        <v>-0.4193</v>
       </c>
       <c r="N32" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4756</v>
+        <v>-0.4571</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0774</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8407</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4756</v>
+        <v>-0.4571</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4756</v>
+        <v>-0.4571</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4756</v>
+        <v>-0.4571</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5265</v>
+        <v>-0.4571</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>252</v>
+        <v>103</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5265</v>
+        <v>-0.4571</v>
       </c>
       <c r="N33" t="n">
-        <v>252</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6122</v>
+        <v>-0.603</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0997</v>
+        <v>-0.0982</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9029</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6122</v>
+        <v>-0.603</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6122</v>
+        <v>-0.603</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6122</v>
+        <v>-0.603</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6122</v>
+        <v>-0.6191</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6122</v>
+        <v>-0.6191</v>
       </c>
       <c r="N34" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6254</v>
+        <v>-0.6267</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1018</v>
+        <v>-0.102</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9089</v>
+        <v>-0.8913</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6254</v>
+        <v>-0.6267</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6254</v>
+        <v>-0.6267</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6254</v>
+        <v>-0.6267</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6415</v>
+        <v>-0.6267</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6415</v>
+        <v>-0.6267</v>
       </c>
       <c r="N35" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1417</v>
+        <v>-0.1411</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0205</v>
+        <v>-1.0005</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9638</v>
+        <v>-0.9628</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9638</v>
+        <v>-0.9628</v>
       </c>
       <c r="N36" t="n">
         <v>252</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0248</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1668</v>
+        <v>-0.154</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0907</v>
+        <v>-1.0368</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0248</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0248</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0248</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0512</v>
+        <v>-0.9714</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0512</v>
+        <v>-0.9714</v>
       </c>
       <c r="N37" t="n">
         <v>162</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1749</v>
+        <v>-0.1712</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1133</v>
+        <v>-1.0848</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0745</v>
+        <v>-1.0515</v>
       </c>
       <c r="N38" t="n">
         <v>103</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1943</v>
+        <v>-1.1706</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1944</v>
+        <v>-0.1906</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1679</v>
+        <v>-1.1391</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1943</v>
+        <v>-1.1706</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1943</v>
+        <v>-1.1706</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1943</v>
+        <v>-1.1706</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.289</v>
+        <v>-1.267</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.289</v>
+        <v>-1.267</v>
       </c>
       <c r="N39" t="n">
         <v>166</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3868</v>
+        <v>-1.3856</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2258</v>
+        <v>-0.2256</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2555</v>
+        <v>-1.237</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3868</v>
+        <v>-1.3856</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3868</v>
+        <v>-1.3856</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3868</v>
+        <v>-1.3856</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5749</v>
+        <v>-1.5809</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5749</v>
+        <v>-1.5809</v>
       </c>
       <c r="N40" t="n">
         <v>297</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5055</v>
+        <v>-1.4257</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2451</v>
+        <v>-0.2321</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3095</v>
+        <v>-1.2553</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5055</v>
+        <v>-1.4257</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5055</v>
+        <v>-1.4257</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5055</v>
+        <v>-1.4257</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7097</v>
+        <v>-1.6267</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7097</v>
+        <v>-1.6267</v>
       </c>
       <c r="N41" t="n">
         <v>297</v>
@@ -2429,10 +2429,10 @@
         <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5125</v>
+        <v>0.4437</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5125</v>
+        <v>0.4437</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3059</v>
+        <v>0.2507</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3059</v>
+        <v>0.2507</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1771</v>
+        <v>0.1383</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1771</v>
+        <v>0.1383</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.008</v>
+        <v>-0.0058</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4817</v>
+        <v>0.4229</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4817</v>
+        <v>0.4229</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1687</v>
+        <v>0.1319</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1687</v>
+        <v>0.1319</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0733</v>
+        <v>-0.0587</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0733</v>
+        <v>-0.0587</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0868</v>
+        <v>-0.0709</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0868</v>
+        <v>-0.0709</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.85</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2024</v>
+        <v>-0.1817</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2024</v>
+        <v>-0.1817</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.364</v>
+        <v>0.3029</v>
       </c>
       <c r="J12" t="n">
-        <v>10.92</v>
+        <v>9.087</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.19</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3023</v>
+        <v>0.2465</v>
       </c>
       <c r="J13" t="n">
-        <v>9.069000000000001</v>
+        <v>7.395</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0291</v>
+        <v>0.0192</v>
       </c>
       <c r="J14" t="n">
-        <v>0.873</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0616</v>
+        <v>-0.0481</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.848</v>
+        <v>-1.443</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.82</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2365</v>
+        <v>-0.2163</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.095</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7705</v>
+        <v>0.7138</v>
       </c>
       <c r="J17" t="n">
-        <v>23.115</v>
+        <v>21.414</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4081</v>
+        <v>0.354</v>
       </c>
       <c r="J18" t="n">
-        <v>12.243</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3418</v>
+        <v>0.2919</v>
       </c>
       <c r="J19" t="n">
-        <v>10.254</v>
+        <v>8.757</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2164</v>
+        <v>0.1779</v>
       </c>
       <c r="J20" t="n">
-        <v>6.492</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2444</v>
+        <v>-0.2251</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.332</v>
+        <v>-6.753</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4888</v>
+        <v>0.4302</v>
       </c>
       <c r="J22" t="n">
-        <v>14.1752</v>
+        <v>12.4758</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0016</v>
+        <v>0.0007</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0464</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0418</v>
+        <v>-0.032</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2122</v>
+        <v>-0.928</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1677</v>
+        <v>-0.1476</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.8633</v>
+        <v>-4.2804</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2307</v>
+        <v>-0.2104</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.6903</v>
+        <v>-6.1016</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4034</v>
+        <v>0.341</v>
       </c>
       <c r="J27" t="n">
-        <v>11.6986</v>
+        <v>9.888999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3922</v>
+        <v>0.3307</v>
       </c>
       <c r="J28" t="n">
-        <v>11.3738</v>
+        <v>9.590299999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3581</v>
+        <v>0.2994</v>
       </c>
       <c r="J29" t="n">
-        <v>10.3849</v>
+        <v>8.682600000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2128</v>
+        <v>0.1704</v>
       </c>
       <c r="J30" t="n">
-        <v>6.1712</v>
+        <v>4.9416</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.98</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0569</v>
+        <v>-0.0446</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.6501</v>
+        <v>-1.2934</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.26</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5288</v>
+        <v>0.4693</v>
       </c>
       <c r="J32" t="n">
-        <v>15.864</v>
+        <v>14.079</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2096</v>
+        <v>0.1679</v>
       </c>
       <c r="J33" t="n">
-        <v>6.288</v>
+        <v>5.037</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0439</v>
+        <v>-0.0332</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.317</v>
+        <v>-0.996</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.96</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.217</v>
+        <v>-1.776</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2441</v>
+        <v>-0.224</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.323</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.66</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7932</v>
+        <v>0.7236</v>
       </c>
       <c r="J37" t="n">
-        <v>23.796</v>
+        <v>21.708</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3724</v>
+        <v>0.3119</v>
       </c>
       <c r="J38" t="n">
-        <v>11.172</v>
+        <v>9.356999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1293</v>
+        <v>0.0989</v>
       </c>
       <c r="J39" t="n">
-        <v>3.879</v>
+        <v>2.967</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.06</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1134</v>
+        <v>0.0858</v>
       </c>
       <c r="J40" t="n">
-        <v>3.402</v>
+        <v>2.574</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3233</v>
+        <v>-0.3082</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.699</v>
+        <v>-9.246</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7755</v>
+        <v>0.7473</v>
       </c>
       <c r="J42" t="n">
-        <v>21.714</v>
+        <v>20.9244</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5773</v>
+        <v>0.5376</v>
       </c>
       <c r="J43" t="n">
-        <v>16.1644</v>
+        <v>15.0528</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1748</v>
+        <v>-0.1418</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.8944</v>
+        <v>-3.9704</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.92</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2943</v>
+        <v>-0.2535</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.240399999999999</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5945</v>
+        <v>-0.5557</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.646</v>
+        <v>-15.5596</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.819</v>
+        <v>0.7658</v>
       </c>
       <c r="J47" t="n">
-        <v>22.932</v>
+        <v>21.4424</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.09</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2233</v>
+        <v>0.1815</v>
       </c>
       <c r="J48" t="n">
-        <v>6.2524</v>
+        <v>5.082</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0475</v>
+        <v>-0.0359</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.33</v>
+        <v>-1.0052</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.141</v>
+        <v>-0.1214</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.948</v>
+        <v>-3.3992</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1639</v>
+        <v>-0.1436</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.5892</v>
+        <v>-4.0208</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0964</v>
+        <v>1.1082</v>
       </c>
       <c r="J52" t="n">
-        <v>30.6992</v>
+        <v>31.0296</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.32</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8132</v>
+        <v>0.7877</v>
       </c>
       <c r="J53" t="n">
-        <v>22.7696</v>
+        <v>22.0556</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5352</v>
+        <v>0.4966</v>
       </c>
       <c r="J54" t="n">
-        <v>14.9856</v>
+        <v>13.9048</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3102</v>
+        <v>-0.2689</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.685600000000001</v>
+        <v>-7.5292</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.67</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8942</v>
+        <v>-0.8811</v>
       </c>
       <c r="J56" t="n">
-        <v>-25.0376</v>
+        <v>-24.6708</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2228</v>
+        <v>0.1787</v>
       </c>
       <c r="J57" t="n">
-        <v>6.2384</v>
+        <v>5.0036</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.05</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1571</v>
+        <v>0.121</v>
       </c>
       <c r="J58" t="n">
-        <v>4.3988</v>
+        <v>3.388</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0694</v>
+        <v>-0.0566</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.9432</v>
+        <v>-1.5848</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.6684</v>
+        <v>-2.2344</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3427</v>
+        <v>-0.3272</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.595599999999999</v>
+        <v>-9.1616</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2071</v>
+        <v>-0.1919</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.3491</v>
+        <v>-4.0299</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2176</v>
+        <v>-0.2027</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.5696</v>
+        <v>-4.2567</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.62</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3848</v>
+        <v>-0.3737</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.0808</v>
+        <v>-7.8477</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.58</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4201</v>
+        <v>-0.411</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.822100000000001</v>
+        <v>-8.631</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4378</v>
+        <v>-0.4299</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.1938</v>
+        <v>-9.027900000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.89</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5526</v>
+        <v>1.5879</v>
       </c>
       <c r="J67" t="n">
-        <v>32.6046</v>
+        <v>33.3459</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.6</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1963</v>
+        <v>1.2133</v>
       </c>
       <c r="J68" t="n">
-        <v>25.1223</v>
+        <v>25.4793</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.46</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0116</v>
+        <v>1.0182</v>
       </c>
       <c r="J69" t="n">
-        <v>21.2436</v>
+        <v>21.3822</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.3</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7229</v>
+        <v>0.7047</v>
       </c>
       <c r="J70" t="n">
-        <v>15.1809</v>
+        <v>14.7987</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3893</v>
+        <v>-0.3553</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.1753</v>
+        <v>-7.4613</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4268</v>
+        <v>0.3618</v>
       </c>
       <c r="J72" t="n">
-        <v>11.9504</v>
+        <v>10.1304</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3922</v>
+        <v>0.3294</v>
       </c>
       <c r="J73" t="n">
-        <v>10.9816</v>
+        <v>9.2232</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3207</v>
+        <v>0.2637</v>
       </c>
       <c r="J74" t="n">
-        <v>8.9796</v>
+        <v>7.3836</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0063</v>
+        <v>-0.0043</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.1764</v>
+        <v>-0.1204</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3646</v>
+        <v>-0.3521</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.2088</v>
+        <v>-9.8588</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3773</v>
+        <v>0.3718</v>
       </c>
       <c r="J77" t="n">
-        <v>10.5644</v>
+        <v>10.4104</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3512</v>
+        <v>0.3432</v>
       </c>
       <c r="J78" t="n">
-        <v>9.833600000000001</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.02</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0567</v>
+        <v>0.0457</v>
       </c>
       <c r="J79" t="n">
-        <v>1.5876</v>
+        <v>1.2796</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0868</v>
+        <v>-0.0709</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.4304</v>
+        <v>-1.9852</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.64</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4028</v>
+        <v>-0.3929</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.2784</v>
+        <v>-11.0012</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5431</v>
+        <v>0.4835</v>
       </c>
       <c r="J82" t="n">
-        <v>19.5516</v>
+        <v>17.406</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.27</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5274</v>
+        <v>0.4681</v>
       </c>
       <c r="J83" t="n">
-        <v>18.9864</v>
+        <v>16.8516</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.16</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3472</v>
+        <v>0.2953</v>
       </c>
       <c r="J84" t="n">
-        <v>12.4992</v>
+        <v>10.6308</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.03</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0902</v>
+        <v>0.0684</v>
       </c>
       <c r="J85" t="n">
-        <v>3.2472</v>
+        <v>2.4624</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3185</v>
+        <v>-0.3025</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.466</v>
+        <v>-10.89</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5404</v>
       </c>
       <c r="J87" t="n">
-        <v>20.8836</v>
+        <v>19.4544</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2259</v>
+        <v>0.1904</v>
       </c>
       <c r="J88" t="n">
-        <v>8.132400000000001</v>
+        <v>6.8544</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.196</v>
+        <v>0.163</v>
       </c>
       <c r="J89" t="n">
-        <v>7.056</v>
+        <v>5.868</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2924</v>
+        <v>-0.2517</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.5264</v>
+        <v>-9.061199999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3731</v>
+        <v>-0.3303</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.4316</v>
+        <v>-11.8908</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.77</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.239</v>
+        <v>-0.2247</v>
       </c>
       <c r="J92" t="n">
-        <v>-5.019</v>
+        <v>-4.7187</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2794</v>
+        <v>-0.2669</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.8674</v>
+        <v>-5.6049</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3715</v>
+        <v>-0.3617</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.8015</v>
+        <v>-7.5957</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.58</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.414</v>
+        <v>-0.4055</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.694000000000001</v>
+        <v>-8.515499999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.43</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5458</v>
+        <v>-0.5494</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.4618</v>
+        <v>-11.5374</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.85</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5019</v>
+        <v>1.5335</v>
       </c>
       <c r="J97" t="n">
-        <v>31.5399</v>
+        <v>32.2035</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2322</v>
+        <v>1.2504</v>
       </c>
       <c r="J98" t="n">
-        <v>25.8762</v>
+        <v>26.2584</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.46</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0105</v>
+        <v>1.0176</v>
       </c>
       <c r="J99" t="n">
-        <v>21.2205</v>
+        <v>21.3696</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5547</v>
+        <v>0.5279</v>
       </c>
       <c r="J100" t="n">
-        <v>11.6487</v>
+        <v>11.0859</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.07</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1895</v>
+        <v>0.1584</v>
       </c>
       <c r="J101" t="n">
-        <v>3.9795</v>
+        <v>3.3264</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3261</v>
+        <v>0.274</v>
       </c>
       <c r="J102" t="n">
-        <v>8.8047</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0202</v>
+        <v>-0.015</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.5454</v>
+        <v>-0.405</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.5019</v>
+        <v>-3.0267</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.141</v>
+        <v>-0.1227</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.807</v>
+        <v>-3.3129</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.9559</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.79</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4988</v>
+        <v>1.5366</v>
       </c>
       <c r="J107" t="n">
-        <v>40.4676</v>
+        <v>41.4882</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7808</v>
+        <v>0.754</v>
       </c>
       <c r="J108" t="n">
-        <v>21.0816</v>
+        <v>20.358</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2058</v>
+        <v>0.177</v>
       </c>
       <c r="J109" t="n">
-        <v>5.5566</v>
+        <v>4.779</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0272</v>
+        <v>-0.0217</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.5859</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.9144</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.9183</v>
+        <v>-24.6888</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4207</v>
+        <v>0.365</v>
       </c>
       <c r="J112" t="n">
-        <v>14.7245</v>
+        <v>12.775</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3846</v>
+        <v>0.33</v>
       </c>
       <c r="J113" t="n">
-        <v>13.461</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.96</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0673</v>
+        <v>-0.0552</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.3555</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3307</v>
+        <v>-0.3143</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.5745</v>
+        <v>-11.0005</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4476</v>
+        <v>-0.4416</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.666</v>
+        <v>-15.456</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2757</v>
+        <v>1.2991</v>
       </c>
       <c r="J117" t="n">
-        <v>44.6495</v>
+        <v>45.4685</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3525</v>
+        <v>0.3131</v>
       </c>
       <c r="J118" t="n">
-        <v>12.3375</v>
+        <v>10.9585</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0893</v>
+        <v>0.0706</v>
       </c>
       <c r="J119" t="n">
-        <v>3.1255</v>
+        <v>2.471</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1124</v>
+        <v>-0.0861</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.934</v>
+        <v>-3.0135</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.8872</v>
+        <v>-0.8722</v>
       </c>
       <c r="J121" t="n">
-        <v>-31.052</v>
+        <v>-30.527</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3289</v>
+        <v>0.2762</v>
       </c>
       <c r="J122" t="n">
-        <v>11.5115</v>
+        <v>9.667</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3104</v>
+        <v>0.2591</v>
       </c>
       <c r="J123" t="n">
-        <v>10.864</v>
+        <v>9.0685</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1251</v>
+        <v>0.0946</v>
       </c>
       <c r="J124" t="n">
-        <v>4.3785</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.01</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0437</v>
+        <v>0.0295</v>
       </c>
       <c r="J125" t="n">
-        <v>1.5295</v>
+        <v>1.0325</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3837</v>
+        <v>-0.3719</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.4295</v>
+        <v>-13.0165</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.4</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9645</v>
+        <v>0.955</v>
       </c>
       <c r="J127" t="n">
-        <v>33.7575</v>
+        <v>33.425</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6405</v>
+        <v>0.6057</v>
       </c>
       <c r="J128" t="n">
-        <v>22.4175</v>
+        <v>21.1995</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.14</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4174</v>
+        <v>0.38</v>
       </c>
       <c r="J129" t="n">
-        <v>14.609</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2668</v>
+        <v>0.234</v>
       </c>
       <c r="J130" t="n">
-        <v>9.337999999999999</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5444</v>
+        <v>-0.5051</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.054</v>
+        <v>-17.6785</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.73</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8288</v>
+        <v>0.7577</v>
       </c>
       <c r="J132" t="n">
-        <v>19.8912</v>
+        <v>18.1848</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>0.618</v>
+        <v>0.5475</v>
       </c>
       <c r="J133" t="n">
-        <v>14.832</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.32</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4253</v>
+        <v>0.3646</v>
       </c>
       <c r="J134" t="n">
-        <v>10.2072</v>
+        <v>8.750400000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.159</v>
+        <v>0.1246</v>
       </c>
       <c r="J135" t="n">
-        <v>3.816</v>
+        <v>2.9904</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0828</v>
+        <v>-0.0693</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.9872</v>
+        <v>-1.6632</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1981</v>
+        <v>0.1937</v>
       </c>
       <c r="J137" t="n">
-        <v>4.7544</v>
+        <v>4.6488</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.83</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1952</v>
+        <v>-0.1797</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.6848</v>
+        <v>-4.3128</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2559</v>
+        <v>-0.2408</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.1416</v>
+        <v>-5.7792</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5057</v>
+        <v>-0.5049</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.1368</v>
+        <v>-12.1176</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.47</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5232</v>
+        <v>-0.5246</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.5568</v>
+        <v>-12.5904</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6475</v>
+        <v>0.5948</v>
       </c>
       <c r="J142" t="n">
-        <v>15.54</v>
+        <v>14.2752</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0598</v>
+        <v>0.0414</v>
       </c>
       <c r="J143" t="n">
-        <v>1.4352</v>
+        <v>0.9936</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.15</v>
+        <v>-0.132</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.6</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1923</v>
+        <v>-0.1728</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.6152</v>
+        <v>-4.1472</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5855</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.7784</v>
+        <v>-14.052</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.87</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5612</v>
+        <v>1.5996</v>
       </c>
       <c r="J147" t="n">
-        <v>37.4688</v>
+        <v>38.3904</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.38</v>
       </c>
       <c r="I148" t="n">
-        <v>0.893</v>
+        <v>0.8788</v>
       </c>
       <c r="J148" t="n">
-        <v>21.432</v>
+        <v>21.0912</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.37</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8741</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>20.9784</v>
+        <v>20.6016</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.109</v>
+        <v>-0.0892</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.616</v>
+        <v>-2.1408</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5223</v>
+        <v>-0.486</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.5352</v>
+        <v>-11.664</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.9</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1132</v>
+        <v>-0.0974</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.4904</v>
+        <v>-2.1428</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.137</v>
+        <v>-0.1212</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.014</v>
+        <v>-2.6664</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.64</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3715</v>
+        <v>-0.3589</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.173</v>
+        <v>-7.8958</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.59</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.416</v>
+        <v>-0.4061</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.151999999999999</v>
+        <v>-8.934200000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4602</v>
+        <v>-0.4541</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.1244</v>
+        <v>-9.9902</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.8</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4461</v>
+        <v>1.4738</v>
       </c>
       <c r="J157" t="n">
-        <v>31.8142</v>
+        <v>32.4236</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.77</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4095</v>
+        <v>1.435</v>
       </c>
       <c r="J158" t="n">
-        <v>31.009</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.58</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1722</v>
+        <v>1.1884</v>
       </c>
       <c r="J159" t="n">
-        <v>25.7884</v>
+        <v>26.1448</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4232</v>
+        <v>0.3919</v>
       </c>
       <c r="J160" t="n">
-        <v>9.3104</v>
+        <v>8.6218</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6579</v>
+        <v>-0.6327</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.4738</v>
+        <v>-13.9194</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2079</v>
+        <v>1.2318</v>
       </c>
       <c r="J162" t="n">
-        <v>35.0291</v>
+        <v>35.7222</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2895</v>
+        <v>0.2493</v>
       </c>
       <c r="J163" t="n">
-        <v>8.3955</v>
+        <v>7.2297</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4177</v>
+        <v>-0.3748</v>
       </c>
       <c r="J164" t="n">
-        <v>-12.1133</v>
+        <v>-10.8692</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.83</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5154</v>
+        <v>-0.4736</v>
       </c>
       <c r="J165" t="n">
-        <v>-14.9466</v>
+        <v>-13.7344</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.65</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.913</v>
+        <v>-0.8986</v>
       </c>
       <c r="J166" t="n">
-        <v>-26.477</v>
+        <v>-26.0594</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.22</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4519</v>
+        <v>0.3942</v>
       </c>
       <c r="J167" t="n">
-        <v>13.1051</v>
+        <v>11.4318</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4519</v>
+        <v>0.3942</v>
       </c>
       <c r="J168" t="n">
-        <v>13.1051</v>
+        <v>11.4318</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.21</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4355</v>
+        <v>0.3783</v>
       </c>
       <c r="J169" t="n">
-        <v>12.6295</v>
+        <v>10.9707</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0781</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.2649</v>
+        <v>-1.8183</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3072</v>
+        <v>-0.2902</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.908799999999999</v>
+        <v>-8.415800000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1197</v>
+        <v>1.1319</v>
       </c>
       <c r="J172" t="n">
-        <v>32.4713</v>
+        <v>32.8251</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.29</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7342</v>
+        <v>0.7057</v>
       </c>
       <c r="J173" t="n">
-        <v>21.2918</v>
+        <v>20.4653</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.13</v>
       </c>
       <c r="I174" t="n">
-        <v>0.387</v>
+        <v>0.3525</v>
       </c>
       <c r="J174" t="n">
-        <v>11.223</v>
+        <v>10.2225</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.04</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1392</v>
+        <v>0.1154</v>
       </c>
       <c r="J175" t="n">
-        <v>4.0368</v>
+        <v>3.3466</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.99</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.092</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-2.668</v>
+        <v>-2.059</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.315</v>
+        <v>0.2633</v>
       </c>
       <c r="J177" t="n">
-        <v>9.135</v>
+        <v>7.6357</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0464</v>
+        <v>0.031</v>
       </c>
       <c r="J178" t="n">
-        <v>1.3456</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0025</v>
+        <v>0.0012</v>
       </c>
       <c r="J179" t="n">
-        <v>0.0725</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.95</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0842</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.4418</v>
+        <v>-2.0039</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2697</v>
+        <v>-0.2503</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.8213</v>
+        <v>-7.2587</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6611</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>27.7662</v>
+        <v>25.2966</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.13</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3007</v>
+        <v>0.251</v>
       </c>
       <c r="J183" t="n">
-        <v>12.6294</v>
+        <v>10.542</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0689</v>
+        <v>0.0504</v>
       </c>
       <c r="J184" t="n">
-        <v>2.8938</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0619</v>
+        <v>-0.0484</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.5998</v>
+        <v>-2.0328</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2765</v>
+        <v>-0.2577</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.613</v>
+        <v>-10.8234</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.115</v>
+        <v>1.132</v>
       </c>
       <c r="J187" t="n">
-        <v>46.83</v>
+        <v>47.544</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.17</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5148</v>
+        <v>0.473</v>
       </c>
       <c r="J188" t="n">
-        <v>21.6216</v>
+        <v>19.866</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2892</v>
+        <v>-0.249</v>
       </c>
       <c r="J189" t="n">
-        <v>-12.1464</v>
+        <v>-10.458</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.82</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5425</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-22.785</v>
+        <v>-21.063</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8953</v>
+        <v>-0.8794</v>
       </c>
       <c r="J191" t="n">
-        <v>-37.6026</v>
+        <v>-36.9348</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.66</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7798</v>
+        <v>0.7086</v>
       </c>
       <c r="J192" t="n">
-        <v>18.7152</v>
+        <v>17.0064</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.55</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6717</v>
+        <v>0.5996</v>
       </c>
       <c r="J193" t="n">
-        <v>16.1208</v>
+        <v>14.3904</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.05</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0907</v>
+        <v>0.0673</v>
       </c>
       <c r="J194" t="n">
-        <v>2.1768</v>
+        <v>1.6152</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1295</v>
+        <v>-0.1113</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.108</v>
+        <v>-2.6712</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.93</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1295</v>
+        <v>-0.1113</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.108</v>
+        <v>-2.6712</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.09</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2285</v>
+        <v>0.2188</v>
       </c>
       <c r="J197" t="n">
-        <v>5.484</v>
+        <v>5.2512</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0709</v>
+        <v>0.0631</v>
       </c>
       <c r="J198" t="n">
-        <v>1.7016</v>
+        <v>1.5144</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.75</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.28</v>
+        <v>-0.2629</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.72</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4166</v>
+        <v>-0.4064</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.9984</v>
+        <v>-9.7536</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.49</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.513</v>
+        <v>-0.5137</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.312</v>
+        <v>-12.3288</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.88</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1497</v>
+        <v>-0.1341</v>
       </c>
       <c r="J202" t="n">
-        <v>-3.1437</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.84</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.193</v>
+        <v>-0.1767</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.053</v>
+        <v>-3.7107</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2331</v>
+        <v>-0.2163</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.8951</v>
+        <v>-4.5423</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.73</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2979</v>
+        <v>-0.2813</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.2559</v>
+        <v>-5.9073</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.362</v>
+        <v>-0.3479</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.602</v>
+        <v>-7.3059</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.76</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4281</v>
+        <v>1.4558</v>
       </c>
       <c r="J207" t="n">
-        <v>29.9901</v>
+        <v>30.5718</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.25</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6421</v>
+        <v>0.6142</v>
       </c>
       <c r="J208" t="n">
-        <v>13.4841</v>
+        <v>12.8982</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.15</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4221</v>
+        <v>0.3898</v>
       </c>
       <c r="J209" t="n">
-        <v>8.864100000000001</v>
+        <v>8.1858</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3738</v>
+        <v>0.3414</v>
       </c>
       <c r="J210" t="n">
-        <v>7.8498</v>
+        <v>7.1694</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2713</v>
+        <v>0.2403</v>
       </c>
       <c r="J211" t="n">
-        <v>5.6973</v>
+        <v>5.0463</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.61</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2276</v>
+        <v>1.2437</v>
       </c>
       <c r="J212" t="n">
-        <v>30.69</v>
+        <v>31.0925</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.48</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0553</v>
+        <v>1.0634</v>
       </c>
       <c r="J213" t="n">
-        <v>26.3825</v>
+        <v>26.585</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5951</v>
+        <v>0.5674</v>
       </c>
       <c r="J214" t="n">
-        <v>14.8775</v>
+        <v>14.185</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5737</v>
+        <v>0.5453</v>
       </c>
       <c r="J215" t="n">
-        <v>14.3425</v>
+        <v>13.6325</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.04</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1184</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>2.96</v>
+        <v>2.3575</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0794</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.985</v>
+        <v>-1.665</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1171</v>
+        <v>-0.1025</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.9275</v>
+        <v>-2.5625</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.129</v>
+        <v>-0.1139</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.225</v>
+        <v>-2.8475</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.72</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3089</v>
+        <v>-0.2921</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.7225</v>
+        <v>-7.3025</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.488</v>
+        <v>-0.4856</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.2</v>
+        <v>-12.14</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7454</v>
+        <v>0.7199</v>
       </c>
       <c r="J222" t="n">
-        <v>19.3804</v>
+        <v>18.7174</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.29</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7254</v>
+        <v>0.699</v>
       </c>
       <c r="J223" t="n">
-        <v>18.8604</v>
+        <v>18.174</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6249</v>
+        <v>0.5947</v>
       </c>
       <c r="J224" t="n">
-        <v>16.2474</v>
+        <v>15.4622</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.21</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5621</v>
+        <v>0.5305</v>
       </c>
       <c r="J225" t="n">
-        <v>14.6146</v>
+        <v>13.793</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.18</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4962</v>
+        <v>0.4636</v>
       </c>
       <c r="J226" t="n">
-        <v>12.9012</v>
+        <v>12.0536</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.13</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3498</v>
+        <v>0.2994</v>
       </c>
       <c r="J227" t="n">
-        <v>9.094799999999999</v>
+        <v>7.7844</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.02</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1028</v>
+        <v>0.0771</v>
       </c>
       <c r="J228" t="n">
-        <v>2.6728</v>
+        <v>2.0046</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2576</v>
+        <v>-0.2388</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.6976</v>
+        <v>-6.2088</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.74</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2957</v>
+        <v>-0.2778</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.6882</v>
+        <v>-7.2228</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.58</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.441</v>
+        <v>-0.4336</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.466</v>
+        <v>-11.2736</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.43</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0023</v>
+        <v>0.9997</v>
       </c>
       <c r="J232" t="n">
-        <v>26.0598</v>
+        <v>25.9922</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.35</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8541</v>
+        <v>0.8333</v>
       </c>
       <c r="J233" t="n">
-        <v>22.2066</v>
+        <v>21.6658</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8343</v>
+        <v>0.8121</v>
       </c>
       <c r="J234" t="n">
-        <v>21.6918</v>
+        <v>21.1146</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.1</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3112</v>
+        <v>0.2783</v>
       </c>
       <c r="J235" t="n">
-        <v>8.091200000000001</v>
+        <v>7.2358</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.7103</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.1464</v>
+        <v>-18.4678</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.21</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4666</v>
+        <v>0.4093</v>
       </c>
       <c r="J237" t="n">
-        <v>12.1316</v>
+        <v>10.6418</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.05</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1583</v>
+        <v>0.122</v>
       </c>
       <c r="J238" t="n">
-        <v>4.1158</v>
+        <v>3.172</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0214</v>
+        <v>-0.0159</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.5564</v>
+        <v>-0.4134</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.73</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3142</v>
+        <v>-0.2969</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.1692</v>
+        <v>-7.7194</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3236</v>
+        <v>-0.3068</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.413600000000001</v>
+        <v>-7.9768</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2379</v>
+        <v>0.2227</v>
       </c>
       <c r="J242" t="n">
-        <v>5.9475</v>
+        <v>5.5675</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.09</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1783</v>
+        <v>0.162</v>
       </c>
       <c r="J243" t="n">
-        <v>4.4575</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1626</v>
+        <v>0.1464</v>
       </c>
       <c r="J244" t="n">
-        <v>4.065</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0449</v>
+        <v>-0.0339</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.1225</v>
+        <v>-0.8475</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.88</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1721</v>
+        <v>-0.1516</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.3025</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6574</v>
+        <v>0.586</v>
       </c>
       <c r="J247" t="n">
-        <v>16.435</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.18</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2795</v>
+        <v>0.2275</v>
       </c>
       <c r="J248" t="n">
-        <v>6.9875</v>
+        <v>5.6875</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.16</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2546</v>
+        <v>0.2055</v>
       </c>
       <c r="J249" t="n">
-        <v>6.365</v>
+        <v>5.1375</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0208</v>
+        <v>0.0133</v>
       </c>
       <c r="J250" t="n">
-        <v>0.52</v>
+        <v>0.3325</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2638</v>
+        <v>-0.2451</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.595</v>
+        <v>-6.1275</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.46</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0848</v>
+        <v>1.0971</v>
       </c>
       <c r="J252" t="n">
-        <v>32.544</v>
+        <v>32.913</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.12</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3812</v>
+        <v>0.3402</v>
       </c>
       <c r="J253" t="n">
-        <v>11.436</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.01</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0515</v>
+        <v>0.0387</v>
       </c>
       <c r="J254" t="n">
-        <v>1.545</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.241</v>
+        <v>-0.2026</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.23</v>
+        <v>-6.078</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.75</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7117</v>
+        <v>-0.6803</v>
       </c>
       <c r="J256" t="n">
-        <v>-21.351</v>
+        <v>-20.409</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.6</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9604</v>
       </c>
       <c r="J257" t="n">
-        <v>29.895</v>
+        <v>28.812</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1801</v>
+        <v>0.1449</v>
       </c>
       <c r="J258" t="n">
-        <v>5.403</v>
+        <v>4.347</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1801</v>
+        <v>0.1449</v>
       </c>
       <c r="J259" t="n">
-        <v>5.403</v>
+        <v>4.347</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0946</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.838</v>
+        <v>-2.331</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2211</v>
+        <v>-0.2009</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.633</v>
+        <v>-6.027</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.86</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1654</v>
+        <v>-0.1498</v>
       </c>
       <c r="J262" t="n">
-        <v>-4.135</v>
+        <v>-3.745</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.82</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.2081</v>
+        <v>-0.1925</v>
       </c>
       <c r="J263" t="n">
-        <v>-5.2025</v>
+        <v>-4.8125</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.77</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2577</v>
+        <v>-0.2422</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.4425</v>
+        <v>-6.055</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.63</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3841</v>
+        <v>-0.3717</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.602499999999999</v>
+        <v>-9.2925</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.62</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.393</v>
+        <v>-0.3812</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.824999999999999</v>
+        <v>-9.529999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.88</v>
       </c>
       <c r="I267" t="n">
-        <v>1.5611</v>
+        <v>1.5983</v>
       </c>
       <c r="J267" t="n">
-        <v>39.0275</v>
+        <v>39.9575</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0226</v>
+        <v>1.0268</v>
       </c>
       <c r="J268" t="n">
-        <v>25.565</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.34</v>
       </c>
       <c r="I269" t="n">
-        <v>0.8116</v>
+        <v>0.7946</v>
       </c>
       <c r="J269" t="n">
-        <v>20.29</v>
+        <v>19.865</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.04</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1146</v>
+        <v>0.0902</v>
       </c>
       <c r="J270" t="n">
-        <v>2.865</v>
+        <v>2.255</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.98</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1582</v>
+        <v>-0.1332</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.955</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.49</v>
       </c>
       <c r="I272" t="n">
-        <v>1.012</v>
+        <v>1.0242</v>
       </c>
       <c r="J272" t="n">
-        <v>20.24</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.63</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.385</v>
+        <v>-0.3726</v>
       </c>
       <c r="J273" t="n">
-        <v>-7.7</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.58</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4296</v>
+        <v>-0.4206</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.592000000000001</v>
+        <v>-8.412000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.58</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4296</v>
+        <v>-0.4206</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.592000000000001</v>
+        <v>-8.412000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.46</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5346</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.692</v>
+        <v>-10.756</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.58</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1865</v>
+        <v>1.2013</v>
       </c>
       <c r="J277" t="n">
-        <v>23.73</v>
+        <v>24.026</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.49</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0674</v>
+        <v>1.0772</v>
       </c>
       <c r="J278" t="n">
-        <v>21.348</v>
+        <v>21.544</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.37</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8689</v>
+        <v>0.8547</v>
       </c>
       <c r="J279" t="n">
-        <v>17.378</v>
+        <v>17.094</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.31</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7559</v>
+        <v>0.7352</v>
       </c>
       <c r="J280" t="n">
-        <v>15.118</v>
+        <v>14.704</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.89</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4274</v>
+        <v>-0.39</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.548</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0368</v>
+        <v>0.0311</v>
       </c>
       <c r="J282" t="n">
-        <v>0.8096</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0048</v>
+        <v>-0.0003</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.1056</v>
+        <v>-0.0066</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0684</v>
+        <v>-0.0566</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.5048</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.57</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.446</v>
+        <v>-0.4389</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.811999999999999</v>
+        <v>-9.655799999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4548</v>
+        <v>-0.4486</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.0056</v>
+        <v>-9.869199999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.77</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4135</v>
+        <v>1.4392</v>
       </c>
       <c r="J287" t="n">
-        <v>31.097</v>
+        <v>31.6624</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.5</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0713</v>
+        <v>1.0837</v>
       </c>
       <c r="J288" t="n">
-        <v>23.5686</v>
+        <v>23.8414</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.44</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9838</v>
+        <v>0.985</v>
       </c>
       <c r="J289" t="n">
-        <v>21.6436</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.38</v>
       </c>
       <c r="I290" t="n">
-        <v>0.8806</v>
+        <v>0.8709</v>
       </c>
       <c r="J290" t="n">
-        <v>19.3732</v>
+        <v>19.1598</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3848</v>
+        <v>-0.3497</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.4656</v>
+        <v>-7.6934</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.37</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4934</v>
+        <v>0.4254</v>
       </c>
       <c r="J292" t="n">
-        <v>12.8284</v>
+        <v>11.0604</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.21</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3128</v>
+        <v>0.2581</v>
       </c>
       <c r="J293" t="n">
-        <v>8.1328</v>
+        <v>6.7106</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2769</v>
+        <v>0.2261</v>
       </c>
       <c r="J294" t="n">
-        <v>7.1994</v>
+        <v>5.8786</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.24</v>
+        <v>0.1938</v>
       </c>
       <c r="J295" t="n">
-        <v>6.24</v>
+        <v>5.0388</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1128</v>
+        <v>-0.095</v>
       </c>
       <c r="J296" t="n">
-        <v>-2.9328</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.06</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1551</v>
+        <v>0.1388</v>
       </c>
       <c r="J297" t="n">
-        <v>4.0326</v>
+        <v>3.6088</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0892</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.3192</v>
+        <v>-1.9708</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1259</v>
+        <v>-0.11</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.2734</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1374</v>
+        <v>-0.1208</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.5724</v>
+        <v>-3.1408</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.54</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4779</v>
+        <v>-0.475</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.4254</v>
+        <v>-12.35</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.28</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5954</v>
+        <v>0.5405</v>
       </c>
       <c r="J302" t="n">
-        <v>14.2896</v>
+        <v>12.972</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.98</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0358</v>
+        <v>-0.028</v>
       </c>
       <c r="J303" t="n">
-        <v>-0.8592</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2135</v>
+        <v>-0.1936</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.124</v>
+        <v>-4.6464</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2135</v>
+        <v>-0.1936</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.124</v>
+        <v>-4.6464</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.61</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4201</v>
+        <v>-0.411</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.0824</v>
+        <v>-9.864000000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.46</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0573</v>
+        <v>1.0638</v>
       </c>
       <c r="J307" t="n">
-        <v>25.3752</v>
+        <v>25.5312</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.2</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5502</v>
+        <v>0.5139</v>
       </c>
       <c r="J308" t="n">
-        <v>13.2048</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.17</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4837</v>
+        <v>0.4469</v>
       </c>
       <c r="J309" t="n">
-        <v>11.6088</v>
+        <v>10.7256</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.05</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1767</v>
+        <v>0.1498</v>
       </c>
       <c r="J310" t="n">
-        <v>4.2408</v>
+        <v>3.5952</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.91</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3456</v>
+        <v>-0.3041</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.2944</v>
+        <v>-7.2984</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.54</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1315</v>
+        <v>1.1453</v>
       </c>
       <c r="J312" t="n">
-        <v>23.7615</v>
+        <v>24.0513</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.47</v>
       </c>
       <c r="I313" t="n">
-        <v>1.0368</v>
+        <v>1.0432</v>
       </c>
       <c r="J313" t="n">
-        <v>21.7728</v>
+        <v>21.9072</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.35</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8298</v>
+        <v>0.8141</v>
       </c>
       <c r="J314" t="n">
-        <v>17.4258</v>
+        <v>17.0961</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.23</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5911</v>
+        <v>0.5641</v>
       </c>
       <c r="J315" t="n">
-        <v>12.4131</v>
+        <v>11.8461</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.13</v>
       </c>
       <c r="I316" t="n">
-        <v>0.3631</v>
+        <v>0.3311</v>
       </c>
       <c r="J316" t="n">
-        <v>7.6251</v>
+        <v>6.9531</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3556</v>
+        <v>0.3103</v>
       </c>
       <c r="J317" t="n">
-        <v>7.4676</v>
+        <v>6.5163</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.99</v>
       </c>
       <c r="I318" t="n">
-        <v>0.0013</v>
+        <v>0.0094</v>
       </c>
       <c r="J318" t="n">
-        <v>0.0273</v>
+        <v>0.1974</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.077</v>
+        <v>-0.0641</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.617</v>
+        <v>-1.3461</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.44</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5556</v>
+        <v>-0.5624</v>
       </c>
       <c r="J320" t="n">
-        <v>-11.6676</v>
+        <v>-11.8104</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.43</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5641</v>
+        <v>-0.5723</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.8461</v>
+        <v>-12.0183</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.54</v>
       </c>
       <c r="I322" t="n">
-        <v>1.168</v>
+        <v>1.1823</v>
       </c>
       <c r="J322" t="n">
-        <v>30.368</v>
+        <v>30.7398</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.45</v>
       </c>
       <c r="I323" t="n">
-        <v>1.0414</v>
+        <v>1.0454</v>
       </c>
       <c r="J323" t="n">
-        <v>27.0764</v>
+        <v>27.1804</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.04</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1444</v>
+        <v>0.1202</v>
       </c>
       <c r="J324" t="n">
-        <v>3.7544</v>
+        <v>3.1252</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.0268</v>
+        <v>-0.0213</v>
       </c>
       <c r="J325" t="n">
-        <v>-0.6968</v>
+        <v>-0.5538</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6644</v>
+        <v>-0.632</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.2744</v>
+        <v>-16.432</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.05</v>
       </c>
       <c r="I327" t="n">
-        <v>0.1617</v>
+        <v>0.1249</v>
       </c>
       <c r="J327" t="n">
-        <v>4.2042</v>
+        <v>3.2474</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.93</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1064</v>
+        <v>-0.0905</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.7664</v>
+        <v>-2.353</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.91</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.367</v>
+        <v>-2.9094</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1735</v>
+        <v>-0.154</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.511</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.86</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1841</v>
+        <v>-0.1643</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.7866</v>
+        <v>-4.2718</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.3</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6223</v>
+        <v>0.5671</v>
       </c>
       <c r="J332" t="n">
-        <v>16.8021</v>
+        <v>15.3117</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.12</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3086</v>
+        <v>0.2577</v>
       </c>
       <c r="J333" t="n">
-        <v>8.3322</v>
+        <v>6.9579</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.07</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2069</v>
+        <v>0.1647</v>
       </c>
       <c r="J334" t="n">
-        <v>5.5863</v>
+        <v>4.4469</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3588</v>
+        <v>-0.3443</v>
       </c>
       <c r="J335" t="n">
-        <v>-9.6876</v>
+        <v>-9.296099999999999</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.44</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5675</v>
+        <v>-0.5782</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.3225</v>
+        <v>-15.6114</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.82</v>
       </c>
       <c r="I337" t="n">
-        <v>1.5502</v>
+        <v>1.5958</v>
       </c>
       <c r="J337" t="n">
-        <v>41.8554</v>
+        <v>43.0866</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.12</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3711</v>
+        <v>0.334</v>
       </c>
       <c r="J338" t="n">
-        <v>10.0197</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I339" t="n">
-        <v>0.2952</v>
+        <v>0.2607</v>
       </c>
       <c r="J339" t="n">
-        <v>7.9704</v>
+        <v>7.0389</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.86</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4697</v>
+        <v>-0.428</v>
       </c>
       <c r="J340" t="n">
-        <v>-12.6819</v>
+        <v>-11.556</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.75</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7252</v>
+        <v>-0.6964</v>
       </c>
       <c r="J341" t="n">
-        <v>-19.5804</v>
+        <v>-18.8028</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.539</v>
+        <v>0.4793</v>
       </c>
       <c r="J342" t="n">
-        <v>25.872</v>
+        <v>23.0064</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.21</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4413</v>
+        <v>0.3836</v>
       </c>
       <c r="J343" t="n">
-        <v>21.1824</v>
+        <v>18.4128</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0397</v>
+        <v>0.0276</v>
       </c>
       <c r="J344" t="n">
-        <v>1.9056</v>
+        <v>1.3248</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.91</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.139</v>
+        <v>-0.1195</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.672</v>
+        <v>-5.736</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2462</v>
+        <v>-0.2263</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.8176</v>
+        <v>-10.8624</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.27</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J347" t="n">
-        <v>34.5264</v>
+        <v>32.976</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.26</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6979</v>
+        <v>0.6643</v>
       </c>
       <c r="J348" t="n">
-        <v>33.4992</v>
+        <v>31.8864</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.22</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6106</v>
+        <v>0.5728</v>
       </c>
       <c r="J349" t="n">
-        <v>29.3088</v>
+        <v>27.4944</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4847</v>
+        <v>-0.4426</v>
       </c>
       <c r="J350" t="n">
-        <v>-23.2656</v>
+        <v>-21.2448</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.79</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6262</v>
+        <v>-0.5897</v>
       </c>
       <c r="J351" t="n">
-        <v>-30.0576</v>
+        <v>-28.3056</v>
       </c>
     </row>
   </sheetData>
